--- a/Инвентаризация компонентов.xlsx
+++ b/Инвентаризация компонентов.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Расхождения" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Компоненты'!$A$1:$K$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Расхождения'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Компоненты'!$A$1:$K$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Расхождения'!$A$1:$G$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +65,14 @@
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -101,11 +107,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -156,9 +157,6 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -170,6 +168,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -538,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -931,18 +932,18 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>не сделано</t>
+          <t>Templates/VP.svg</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J8" s="5" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Отдельного файла трека влияния в папке нет. По правилам трек влияния кладётся поверх трека Судного дня.</t>
+          <t>Напечатан (подтверждено Alek). По правилам кладётся поверх трека Судного дня.</t>
         </is>
       </c>
     </row>
@@ -1032,23 +1033,23 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>не определён</t>
+          <t>покупные пластиковые бочонки нефти</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>нет носителя</t>
+          <t>покупной компонент, арт не требуется</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J10" s="5" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>10 шт при 8 фракциях. В CW маркер ресурса персональный. Носитель у нас не выбран.</t>
+          <t>Закуплены (подтверждено Alek). В CW маркер ресурса персональный, по 1 на фракцию; у нас общий пул 10 шт.</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1086,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>покупные кубики + наклейки</t>
+          <t>покупные белые чистые кубики + наклейки</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1093,15 +1094,15 @@
           <t>Templates/Saved/Dices Print Sheet.pdf (1 стр.)</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>требует доработки</t>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J11" s="5" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>На листе 80 наклеек (30/25/25 по типам). На 20 кубиков нужно 120 граней — лист не покрывает полный комплект, проверить раскладку.</t>
+          <t>Комплект собран: наклейки нанесены на белые чистые d6 (подтверждено Alek).</t>
         </is>
       </c>
     </row>
@@ -1252,87 +1253,83 @@
           <t>Templates/Saved/Карты скрытого влияния - (формат Mini USA).pdf (4 стр.)</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>требует доработки</t>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J14" s="5" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>В PDF фактически 40 карт: 20×1, 13×2, 7×3. Расходится с правилами и с оригиналом CW. Носитель осознанно заменён с жетонов на карты.</t>
+          <t>Напечатаны. На листе 40 карт (20/13/7) — 4 сверх нормы намеренно, запас под брак резки и печати. Рабочая колода 36 (18/12/6), совпадает с оригиналом CW. Носитель осознанно заменён с жетонов на карты.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>1. Общие компоненты</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Жетон «Контроль»</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Отдельного компонента нет — контроль обозначается пехотинцем поверх врат</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>количество не задано</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>нет в оригинале</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>файл в папке</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>акрил, ⌀20 мм</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Под Акрил/06. Контроль - круглый жетон - ⌀20мм.png</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>требует доработки</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>СВЕРХ ОРИГИНАЛА. В имени файла нет количества. Альфа-канал теперь есть (CLAUDE.md устарел). Сюжетно дублирует ЦУ — по решению перерисовать как локальный ретранслятор (зона сети).</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2. Компоненты фракции</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>2. Компоненты фракции</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Островная Империя — пехотинцы «Рекрут»</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Пехотинцы-послушники (Acolyte Cultists)</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>6 — база и все допы, константа</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>док фракций v2.0</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>миниатюра (закуплена, покрашена)</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Templates/Units/adept.png (арт-референс)</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1342,22 +1339,22 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Островная Империя — пехотинцы «Рекрут»</t>
+          <t>Островная Империя — боевые машины</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Пехотинцы-послушники (Acolyte Cultists)</t>
+          <t>Монстры (Monsters)</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>6 — база и все допы, константа</t>
+          <t>8–10 на фракцию — база и допы</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1367,12 +1364,12 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/adept.png (арт-референс)</t>
+          <t>Templates/Units/Островная Империя/</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
@@ -1381,7 +1378,11 @@
         </is>
       </c>
       <c r="J17" s="5" t="n"/>
-      <c r="K17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Морпех 4, робот «Цунами» 2, танк «Мегалодон» 2</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1391,22 +1392,22 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Островная Империя — боевые машины</t>
+          <t>Островная Империя — боевой робот «Краб» (в PDF карт целей — «C.R.A.B.»)</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Монстры (Monsters)</t>
+          <t>Великий Древний (Great Old One)</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>8–10 на фракцию — база и допы</t>
+          <t>1 — типовое; 2 у Yellow Sign (база), 3 у Daemon Sultan, 0 у The Ancients</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1416,12 +1417,12 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/Островная Империя/</t>
+          <t>Иллюстрации/ (арт-референсы)</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -1432,7 +1433,7 @@
       <c r="J18" s="5" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Морпех 4, робот «Цунами» 2, танк «Мегалодон» 2</t>
+          <t>Написание расходится: CLAUDE.md «Краб», карта цели «C.R.A.B.».</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1445,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Островная Империя — боевой робот «Краб» (в PDF карт целей — «C.R.A.B.»)</t>
+          <t>Островная Империя — планшет фракции</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Великий Древний (Great Old One)</t>
+          <t>Планшет фракции (Faction Card)</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1459,22 +1460,22 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>1 — типовое; 2 у Yellow Sign (база), 3 у Daemon Sultan, 0 у The Ancients</t>
+          <t>1 — база и каждый доп</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>док фракций v2.0</t>
+          <t>правила, §Компоненты</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>планшет, A4 landscape</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Иллюстрации/ (арт-референсы)</t>
+          <t>Templates/Saved/Faction Card — Островная Империя.pdf (2 стр.)</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -1483,11 +1484,7 @@
         </is>
       </c>
       <c r="J19" s="5" t="n"/>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>Написание расходится: CLAUDE.md «Краб», карта цели «C.R.A.B.».</t>
-        </is>
-      </c>
+      <c r="K19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1497,22 +1494,22 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Островная Империя — планшет фракции</t>
+          <t>Островная Империя — карты целей (задач)</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Планшет фракции (Faction Card)</t>
+          <t>Требования к заклинаниям (Spellbook requirements) — слоты на планшете</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>1 — база и каждый доп</t>
+          <t>6 слотов на планшете — база и каждый доп</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1522,12 +1519,12 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>планшет, A4 landscape</t>
+          <t>карта, Mini USA</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Faction Card — Островная Империя.pdf (2 стр.)</t>
+          <t>Templates/Saved/Технологии и задачи.pdf (48 карт целей на 8 фракций)</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -1536,7 +1533,11 @@
         </is>
       </c>
       <c r="J20" s="5" t="n"/>
-      <c r="K20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW условия напечатаны прямо на планшете, отдельных карт нет.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1546,12 +1547,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Островная Империя — карты целей (задач)</t>
+          <t>Островная Империя — карты технологий</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Требования к заклинаниям (Spellbook requirements) — слоты на планшете</t>
+          <t>Книги заклинаний (Spellbooks) — картонные жетоны-накладки</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1561,7 +1562,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>6 слотов на планшете — база и каждый доп</t>
+          <t>6 на фракцию — база (24 на 4 фракции) и каждый доп</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1576,7 +1577,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Технологии и задачи.pdf (48 карт целей на 8 фракций)</t>
+          <t>Templates/Saved/Технологии и задачи.pdf</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -1587,7 +1588,7 @@
       <c r="J21" s="5" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW условия напечатаны прямо на планшете, отдельных карт нет.</t>
+          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW это жетоны, которыми накрывают слоты планшета. Карта должна физически ложиться на слот. Расхождение дока: «Муштра» / «Подготовка».</t>
         </is>
       </c>
     </row>
@@ -1599,22 +1600,22 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Островная Империя — карты технологий</t>
+          <t>Островная Империя — маркер фракции</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Книги заклинаний (Spellbooks) — картонные жетоны-накладки</t>
+          <t>Маркеры фракции (Faction Markers): Doom + Power</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>6 на фракцию — база (24 на 4 фракции) и каждый доп</t>
+          <t>2 на фракцию — база</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1624,12 +1625,12 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>карта, Mini USA</t>
+          <t>акрил, ⌀18 мм</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Технологии и задачи.pdf</t>
+          <t>Под Акрил/07. Жетоны-логотипы, шестигранные - по 1шт - ⌀18мм/Островная Империя.png</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
@@ -1640,7 +1641,7 @@
       <c r="J22" s="5" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW это жетоны, которыми накрывают слоты планшета. Карта должна физически ложиться на слот. Расхождение дока: «Муштра» / «Подготовка».</t>
+          <t>Вариант «плашка с гексом». Альтернатива «символ с обводкой» — Под Акрил/_Логотипы — варианты/.</t>
         </is>
       </c>
     </row>
@@ -1652,48 +1653,48 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Островная Империя — маркер фракции</t>
+          <t>Островная Империя — уникальные жетоны</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Маркеры фракции (Faction Markers): Doom + Power</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>2 на фракцию — база</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>правила, §Компоненты</t>
+          <t>док фракций v2.0</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>акрил, ⌀18 мм</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Под Акрил/07. Жетоны-логотипы, шестигранные - по 1шт - ⌀18мм/Островная Империя.png</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>готово</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Вариант «плашка с гексом». Альтернатива «символ с обводкой» — Под Акрил/_Логотипы — варианты/.</t>
+          <t>Уникальных компонентов у фракции нет.</t>
         </is>
       </c>
     </row>
@@ -1705,22 +1706,22 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Островная Империя — уникальные жетоны</t>
+          <t>Эйркрафт Корпорейшн — пехотинцы «Рекрут»</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Пехотинцы-послушники (Acolyte Cultists)</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6 — база и все допы, константа</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1730,25 +1731,21 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Templates/Units/adept.png (арт-референс)</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J24" s="5" t="n"/>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>Уникальных компонентов у фракции нет.</t>
-        </is>
-      </c>
+      <c r="K24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1758,22 +1755,22 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Эйркрафт Корпорейшн — пехотинцы «Рекрут»</t>
+          <t>Эйркрафт Корпорейшн — боевые машины</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Пехотинцы-послушники (Acolyte Cultists)</t>
+          <t>Монстры (Monsters)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>6 — база и все допы, константа</t>
+          <t>8–10 на фракцию — база и допы</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1783,12 +1780,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/adept.png (арт-референс)</t>
+          <t>Templates/Units/Эйркрафт Корпорейшн/</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
@@ -1797,7 +1794,11 @@
         </is>
       </c>
       <c r="J25" s="5" t="n"/>
-      <c r="K25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>самолёт «Ночной призрак» 3, самолёт «Фантом» 3, робот «Небесный охотник» 2</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1807,22 +1808,22 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Эйркрафт Корпорейшн — боевые машины</t>
+          <t>Эйркрафт Корпорейшн — боевой робот «Спрут»</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Монстры (Monsters)</t>
+          <t>Великий Древний (Great Old One)</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>8–10 на фракцию — база и допы</t>
+          <t>1 — типовое; 2 у Yellow Sign (база), 3 у Daemon Sultan, 0 у The Ancients</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1832,12 +1833,12 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/Эйркрафт Корпорейшн/</t>
+          <t>Иллюстрации/ (арт-референсы)</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -1846,11 +1847,7 @@
         </is>
       </c>
       <c r="J26" s="5" t="n"/>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>самолёт «Ночной призрак» 3, самолёт «Фантом» 3, робот «Небесный охотник» 2</t>
-        </is>
-      </c>
+      <c r="K26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1860,12 +1857,12 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Эйркрафт Корпорейшн — боевой робот «Спрут»</t>
+          <t>Эйркрафт Корпорейшн — планшет фракции</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Великий Древний (Great Old One)</t>
+          <t>Планшет фракции (Faction Card)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1875,22 +1872,22 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>1 — типовое; 2 у Yellow Sign (база), 3 у Daemon Sultan, 0 у The Ancients</t>
+          <t>1 — база и каждый доп</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>док фракций v2.0</t>
+          <t>правила, §Компоненты</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>планшет, A4 landscape</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Иллюстрации/ (арт-референсы)</t>
+          <t>Templates/Saved/Faction Card — Эйркрафт Корпорейшн.pdf (2 стр.)</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -1909,22 +1906,22 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Эйркрафт Корпорейшн — планшет фракции</t>
+          <t>Эйркрафт Корпорейшн — карты целей (задач)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Планшет фракции (Faction Card)</t>
+          <t>Требования к заклинаниям (Spellbook requirements) — слоты на планшете</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>1 — база и каждый доп</t>
+          <t>6 слотов на планшете — база и каждый доп</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1934,12 +1931,12 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>планшет, A4 landscape</t>
+          <t>карта, Mini USA</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Faction Card — Эйркрафт Корпорейшн.pdf (2 стр.)</t>
+          <t>Templates/Saved/Технологии и задачи.pdf (48 карт целей на 8 фракций)</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -1948,7 +1945,11 @@
         </is>
       </c>
       <c r="J28" s="5" t="n"/>
-      <c r="K28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW условия напечатаны прямо на планшете, отдельных карт нет.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1958,12 +1959,12 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Эйркрафт Корпорейшн — карты целей (задач)</t>
+          <t>Эйркрафт Корпорейшн — карты технологий</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Требования к заклинаниям (Spellbook requirements) — слоты на планшете</t>
+          <t>Книги заклинаний (Spellbooks) — картонные жетоны-накладки</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -1973,7 +1974,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>6 слотов на планшете — база и каждый доп</t>
+          <t>6 на фракцию — база (24 на 4 фракции) и каждый доп</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1988,7 +1989,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Технологии и задачи.pdf (48 карт целей на 8 фракций)</t>
+          <t>Templates/Saved/Технологии и задачи.pdf</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
@@ -1999,7 +2000,7 @@
       <c r="J29" s="5" t="n"/>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW условия напечатаны прямо на планшете, отдельных карт нет.</t>
+          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW это жетоны, которыми накрывают слоты планшета. Карта должна физически ложиться на слот.</t>
         </is>
       </c>
     </row>
@@ -2011,22 +2012,22 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Эйркрафт Корпорейшн — карты технологий</t>
+          <t>Эйркрафт Корпорейшн — маркер фракции</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Книги заклинаний (Spellbooks) — картонные жетоны-накладки</t>
+          <t>Маркеры фракции (Faction Markers): Doom + Power</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>6 на фракцию — база (24 на 4 фракции) и каждый доп</t>
+          <t>2 на фракцию — база</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -2036,12 +2037,12 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>карта, Mini USA</t>
+          <t>акрил, ⌀18 мм</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Технологии и задачи.pdf</t>
+          <t>Под Акрил/07. Жетоны-логотипы, шестигранные - по 1шт - ⌀18мм/Эйркрафт Корпорейшн.png</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -2052,7 +2053,7 @@
       <c r="J30" s="5" t="n"/>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW это жетоны, которыми накрывают слоты планшета. Карта должна физически ложиться на слот.</t>
+          <t>Вариант «плашка с гексом». Альтернатива «символ с обводкой» — Под Акрил/_Логотипы — варианты/.</t>
         </is>
       </c>
     </row>
@@ -2064,48 +2065,48 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Эйркрафт Корпорейшн — маркер фракции</t>
+          <t>Эйркрафт Корпорейшн — уникальные жетоны</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Маркеры фракции (Faction Markers): Doom + Power</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>2 на фракцию — база</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>правила, §Компоненты</t>
+          <t>док фракций v2.0</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>акрил, ⌀18 мм</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Под Акрил/07. Жетоны-логотипы, шестигранные - по 1шт - ⌀18мм/Эйркрафт Корпорейшн.png</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>готово</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J31" s="5" t="n"/>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>Вариант «плашка с гексом». Альтернатива «символ с обводкой» — Под Акрил/_Логотипы — варианты/.</t>
+          <t>Уникальных компонентов у фракции нет.</t>
         </is>
       </c>
     </row>
@@ -2117,22 +2118,22 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Эйркрафт Корпорейшн — уникальные жетоны</t>
+          <t>Глобал Петролеум — пехотинцы «Рекрут»</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Пехотинцы-послушники (Acolyte Cultists)</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6 — база и все допы, константа</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -2142,25 +2143,21 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Templates/Units/adept.png (арт-референс)</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J32" s="5" t="n"/>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>Уникальных компонентов у фракции нет.</t>
-        </is>
-      </c>
+      <c r="K32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -2170,22 +2167,22 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Глобал Петролеум — пехотинцы «Рекрут»</t>
+          <t>Глобал Петролеум — боевые машины</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Пехотинцы-послушники (Acolyte Cultists)</t>
+          <t>Монстры (Monsters)</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>6 — база и все допы, константа</t>
+          <t>8–10 на фракцию — база и допы</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -2195,12 +2192,12 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/adept.png (арт-референс)</t>
+          <t>Templates/Units/Глобал Петролеум/</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -2209,7 +2206,11 @@
         </is>
       </c>
       <c r="J33" s="5" t="n"/>
-      <c r="K33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>ББМ «Саранча» 6, моторизированный десантник 4</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -2219,22 +2220,22 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Глобал Петролеум — боевые машины</t>
+          <t>Глобал Петролеум — боевой робот «Пастух» + «Чёрный вихрь»</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Монстры (Monsters)</t>
+          <t>Великий Древний (Great Old One)</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>8–10 на фракцию — база и допы</t>
+          <t>1 — типовое; 2 у Yellow Sign (база), 3 у Daemon Sultan, 0 у The Ancients</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -2244,12 +2245,12 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/Глобал Петролеум/</t>
+          <t>Иллюстрации/ (арт-референсы)</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
@@ -2260,7 +2261,7 @@
       <c r="J34" s="5" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>ББМ «Саранча» 6, моторизированный десантник 4</t>
+          <t>Два боевых робота — прецедент в CW есть (Yellow Sign: Hastur + King in Yellow).</t>
         </is>
       </c>
     </row>
@@ -2272,37 +2273,37 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Глобал Петролеум — боевой робот «Пастух» + «Чёрный вихрь»</t>
+          <t>Глобал Петролеум — планшет фракции</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Великий Древний (Great Old One)</t>
+          <t>Планшет фракции (Faction Card)</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>1 — типовое; 2 у Yellow Sign (база), 3 у Daemon Sultan, 0 у The Ancients</t>
+          <t>1 — база и каждый доп</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>док фракций v2.0</t>
+          <t>правила, §Компоненты</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>планшет, A4 landscape</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Иллюстрации/ (арт-референсы)</t>
+          <t>Templates/Saved/Faction Card — Глобал Петролеум.pdf (2 стр.)</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
@@ -2311,11 +2312,7 @@
         </is>
       </c>
       <c r="J35" s="5" t="n"/>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>Два боевых робота — прецедент в CW есть (Yellow Sign: Hastur + King in Yellow).</t>
-        </is>
-      </c>
+      <c r="K35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -2325,22 +2322,22 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Глобал Петролеум — планшет фракции</t>
+          <t>Глобал Петролеум — карты целей (задач)</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Планшет фракции (Faction Card)</t>
+          <t>Требования к заклинаниям (Spellbook requirements) — слоты на планшете</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>1 — база и каждый доп</t>
+          <t>6 слотов на планшете — база и каждый доп</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -2350,12 +2347,12 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>планшет, A4 landscape</t>
+          <t>карта, Mini USA</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Faction Card — Глобал Петролеум.pdf (2 стр.)</t>
+          <t>Templates/Saved/Технологии и задачи.pdf (48 карт целей на 8 фракций)</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
@@ -2364,7 +2361,11 @@
         </is>
       </c>
       <c r="J36" s="5" t="n"/>
-      <c r="K36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW условия напечатаны прямо на планшете, отдельных карт нет.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -2374,12 +2375,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Глобал Петролеум — карты целей (задач)</t>
+          <t>Глобал Петролеум — карты технологий</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Требования к заклинаниям (Spellbook requirements) — слоты на планшете</t>
+          <t>Книги заклинаний (Spellbooks) — картонные жетоны-накладки</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -2389,7 +2390,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>6 слотов на планшете — база и каждый доп</t>
+          <t>6 на фракцию — база (24 на 4 фракции) и каждый доп</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -2404,7 +2405,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Технологии и задачи.pdf (48 карт целей на 8 фракций)</t>
+          <t>Templates/Saved/Технологии и задачи.pdf</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
@@ -2415,7 +2416,7 @@
       <c r="J37" s="5" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW условия напечатаны прямо на планшете, отдельных карт нет.</t>
+          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW это жетоны, которыми накрывают слоты планшета. Карта должна физически ложиться на слот.</t>
         </is>
       </c>
     </row>
@@ -2427,22 +2428,22 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Глобал Петролеум — карты технологий</t>
+          <t>Глобал Петролеум — маркер фракции</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Книги заклинаний (Spellbooks) — картонные жетоны-накладки</t>
+          <t>Маркеры фракции (Faction Markers): Doom + Power</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>6 на фракцию — база (24 на 4 фракции) и каждый доп</t>
+          <t>2 на фракцию — база</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -2452,12 +2453,12 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>карта, Mini USA</t>
+          <t>акрил, ⌀18 мм</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Технологии и задачи.pdf</t>
+          <t>Под Акрил/07. Жетоны-логотипы, шестигранные - по 1шт - ⌀18мм/Глобал Петролеум.png</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
@@ -2468,7 +2469,7 @@
       <c r="J38" s="5" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW это жетоны, которыми накрывают слоты планшета. Карта должна физически ложиться на слот.</t>
+          <t>Вариант «плашка с гексом». Альтернатива «символ с обводкой» — Под Акрил/_Логотипы — варианты/.</t>
         </is>
       </c>
     </row>
@@ -2480,22 +2481,22 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Глобал Петролеум — маркер фракции</t>
+          <t>Глобал Петролеум — Жетоны «Нефтяная вышка»</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Маркеры фракции (Faction Markers): Doom + Power</t>
+          <t>Аналога нет; ближайшее — 12 жетонов Filth у Абхота (GOO Pack 1, доп.)</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>2 на фракцию — база</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -2505,12 +2506,12 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>акрил, ⌀18 мм</t>
+          <t>акрил, стенд ↕25 мм</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Под Акрил/07. Жетоны-логотипы, шестигранные - по 1шт - ⌀18мм/Глобал Петролеум.png</t>
+          <t>Под Акрил/01. Вышки - стенд - 12шт - ↕️25мм.png</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
@@ -2521,7 +2522,7 @@
       <c r="J39" s="5" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>Вариант «плашка с гексом». Альтернатива «символ с обводкой» — Под Акрил/_Логотипы — варианты/.</t>
+          <t>Правила: 12. Док фракций количество не задаёт. Есть также печатный арт Templates/Вышка Глобал Петролеум - лицо/задник.png</t>
         </is>
       </c>
     </row>
@@ -2533,37 +2534,37 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Глобал Петролеум — Жетоны «Нефтяная вышка»</t>
+          <t>Братство Сингулярности — пехотинцы «Рекрут»</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Аналога нет; ближайшее — 12 жетонов Filth у Абхота (GOO Pack 1, доп.)</t>
+          <t>Пехотинцы-послушники (Acolyte Cultists)</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6 — база и все допы, константа</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>правила, §Компоненты</t>
+          <t>док фракций v2.0</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>акрил, стенд ↕25 мм</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Под Акрил/01. Вышки - стенд - 12шт - ↕️25мм.png</t>
+          <t>Templates/Units/adept.png (арт-референс)</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
@@ -2572,11 +2573,7 @@
         </is>
       </c>
       <c r="J40" s="5" t="n"/>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>Правила: 12. Док фракций количество не задаёт. Есть также печатный арт Templates/Вышка Глобал Петролеум - лицо/задник.png</t>
-        </is>
-      </c>
+      <c r="K40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -2586,12 +2583,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Братство Сингулярности — пехотинцы «Рекрут»</t>
+          <t>Братство Сингулярности — боевые машины</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Пехотинцы-послушники (Acolyte Cultists)</t>
+          <t>Монстры (Monsters)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -2601,7 +2598,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>6 — база и все допы, константа</t>
+          <t>8–10 на фракцию — база и допы</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2611,12 +2608,12 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/adept.png (арт-референс)</t>
+          <t>Templates/Units/Братство Сингулярности/</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
@@ -2625,7 +2622,11 @@
         </is>
       </c>
       <c r="J41" s="5" t="n"/>
-      <c r="K41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>фанатик 3, киборг 3</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -2635,22 +2636,22 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Братство Сингулярности — боевые машины</t>
+          <t>Братство Сингулярности — боевой робот боевого робота нет; мех «Паладин Братства» ×3</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Монстры (Monsters)</t>
+          <t>Великий Древний (Great Old One)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>8–10 на фракцию — база и допы</t>
+          <t>1 — типовое; 2 у Yellow Sign (база), 3 у Daemon Sultan, 0 у The Ancients</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -2660,23 +2661,23 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/Братство Сингулярности/</t>
-        </is>
-      </c>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>готово</t>
+          <t>Иллюстрации/ (арт-референсы)</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J42" s="5" t="n"/>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>фанатик 3, киборг 3</t>
+          <t>Боевого робота нет — вместо него 3 меха. В CW прецедент фракции без Великого Древнего есть (The Ancients).</t>
         </is>
       </c>
     </row>
@@ -2688,22 +2689,22 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Братство Сингулярности — боевой робот боевого робота нет; мех «Паладин Братства» ×3</t>
+          <t>Братство Сингулярности — мехи «Паладин Братства»</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Великий Древний (Great Old One)</t>
+          <t>Аналога нет (отдельный класс Terror — доп. CW-U5)</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>1 — типовое; 2 у Yellow Sign (база), 3 у Daemon Sultan, 0 у The Ancients</t>
+          <t>нет прямого аналога</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -2713,23 +2714,23 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Иллюстрации/ (арт-референсы)</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Templates/Units/Братство Сингулярности/</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J43" s="5" t="n"/>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>Боевого робота нет — вместо него 3 меха. В CW прецедент фракции без Великого Древнего есть (The Ancients).</t>
+          <t>СВЕРХ ОРИГИНАЛА: «мех» — отдельный тип отряда, строится как боевая машина, но неуязвим к эффектам против БМ. В доке местами назван «Шахид» (остаток от Всемирного Халифата).</t>
         </is>
       </c>
     </row>
@@ -2741,37 +2742,37 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Братство Сингулярности — мехи «Паладин Братства»</t>
+          <t>Братство Сингулярности — планшет фракции</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Аналога нет (отдельный класс Terror — доп. CW-U5)</t>
+          <t>Планшет фракции (Faction Card)</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>нет прямого аналога</t>
+          <t>1 — база и каждый доп</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>док фракций v2.0</t>
+          <t>правила, §Компоненты</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>планшет, A4 landscape</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/Братство Сингулярности/</t>
+          <t>Templates/Saved/Faction Card — Братство Сингулярности.pdf (2 стр.)</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
@@ -2780,11 +2781,7 @@
         </is>
       </c>
       <c r="J44" s="5" t="n"/>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>СВЕРХ ОРИГИНАЛА: «мех» — отдельный тип отряда, строится как боевая машина, но неуязвим к эффектам против БМ. В доке местами назван «Шахид» (остаток от Всемирного Халифата).</t>
-        </is>
-      </c>
+      <c r="K44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2794,22 +2791,22 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Братство Сингулярности — планшет фракции</t>
+          <t>Братство Сингулярности — карты целей (задач)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Планшет фракции (Faction Card)</t>
+          <t>Требования к заклинаниям (Spellbook requirements) — слоты на планшете</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1 — база и каждый доп</t>
+          <t>6 слотов на планшете — база и каждый доп</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2819,12 +2816,12 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>планшет, A4 landscape</t>
+          <t>карта, Mini USA</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Faction Card — Братство Сингулярности.pdf (2 стр.)</t>
+          <t>Templates/Saved/Технологии и задачи.pdf (48 карт целей на 8 фракций)</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
@@ -2833,7 +2830,11 @@
         </is>
       </c>
       <c r="J45" s="5" t="n"/>
-      <c r="K45" s="3" t="inlineStr"/>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW условия напечатаны прямо на планшете, отдельных карт нет.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -2843,12 +2844,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Братство Сингулярности — карты целей (задач)</t>
+          <t>Братство Сингулярности — карты технологий</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Требования к заклинаниям (Spellbook requirements) — слоты на планшете</t>
+          <t>Книги заклинаний (Spellbooks) — картонные жетоны-накладки</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -2858,7 +2859,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>6 слотов на планшете — база и каждый доп</t>
+          <t>6 на фракцию — база (24 на 4 фракции) и каждый доп</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -2873,7 +2874,7 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Технологии и задачи.pdf (48 карт целей на 8 фракций)</t>
+          <t>Templates/Saved/Технологии и задачи.pdf</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
@@ -2884,7 +2885,7 @@
       <c r="J46" s="5" t="n"/>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW условия напечатаны прямо на планшете, отдельных карт нет.</t>
+          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW это жетоны, которыми накрывают слоты планшета. Карта должна физически ложиться на слот. Оглавление дока даёт другой набор технологий (Агитация, Невосстановимость, Профсоюзная активность, Массовые протесты) — остаток от Всемирного Халифата.</t>
         </is>
       </c>
     </row>
@@ -2896,22 +2897,22 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Братство Сингулярности — карты технологий</t>
+          <t>Братство Сингулярности — маркер фракции</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Книги заклинаний (Spellbooks) — картонные жетоны-накладки</t>
+          <t>Маркеры фракции (Faction Markers): Doom + Power</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>6 на фракцию — база (24 на 4 фракции) и каждый доп</t>
+          <t>2 на фракцию — база</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -2921,12 +2922,12 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>карта, Mini USA</t>
+          <t>акрил, ⌀18 мм</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Технологии и задачи.pdf</t>
+          <t>Под Акрил/07. Жетоны-логотипы, шестигранные - по 1шт - ⌀18мм/Братство Сингулярности.png</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -2937,7 +2938,7 @@
       <c r="J47" s="5" t="n"/>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW это жетоны, которыми накрывают слоты планшета. Карта должна физически ложиться на слот. Оглавление дока даёт другой набор технологий (Агитация, Невосстановимость, Профсоюзная активность, Массовые протесты) — остаток от Всемирного Халифата.</t>
+          <t>Вариант «плашка с гексом». Альтернатива «символ с обводкой» — Под Акрил/_Логотипы — варианты/.</t>
         </is>
       </c>
     </row>
@@ -2949,22 +2950,22 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Братство Сингулярности — маркер фракции</t>
+          <t>Братство Сингулярности — Жетоны «Община»</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Маркеры фракции (Faction Markers): Doom + Power</t>
+          <t>Соборы (Cathedrals) — 4 шт. у фракции The Ancients (Onslaught 3)</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>2 на фракцию — база</t>
+          <t>4 — доп. CW-F6</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -2974,12 +2975,12 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>акрил, ⌀18 мм</t>
+          <t>картон</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Под Акрил/07. Жетоны-логотипы, шестигранные - по 1шт - ⌀18мм/Братство Сингулярности.png</t>
+          <t>Templates/Saved/Factory Tokens v2.pdf, стр. 2 (8 плиток = 4 двусторонних жетона)</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -2990,7 +2991,7 @@
       <c r="J48" s="5" t="n"/>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>Вариант «плашка с гексом». Альтернатива «символ с обводкой» — Под Акрил/_Логотипы — варианты/.</t>
+          <t>Готовы (подтверждено Alek). 8 плиток на листе — это лица и рубашки 4 двусторонних жетонов. Акриловая версия — низкий приоритет.</t>
         </is>
       </c>
     </row>
@@ -3002,50 +3003,46 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Братство Сингулярности — Жетоны «Община»</t>
+          <t>Клонэйд Ресёрч — пехотинцы «Рекрут»</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Соборы (Cathedrals) — 4 шт. у фракции The Ancients (Onslaught 3)</t>
+          <t>Пехотинцы-послушники (Acolyte Cultists)</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>4 — доп. CW-F6</t>
+          <t>6 — база и все допы, константа</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>правила, §Компоненты</t>
+          <t>док фракций v2.0</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>картон</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Factory Tokens v2.pdf, стр. 2 (8 плиток: 4 с символом + 4 без)</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>требует доработки</t>
+          <t>Templates/Units/adept.png (арт-референс)</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J49" s="5" t="n"/>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>Правила: 4. Док фракций: «3 символьные + 1 бессимвольная» = 4. В PDF 8 плиток. Акриловая версия — низкий приоритет.</t>
-        </is>
-      </c>
+      <c r="K49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -3055,22 +3052,22 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Клонэйд Ресёрч — пехотинцы «Рекрут»</t>
+          <t>Клонэйд Ресёрч — боевые машины</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Пехотинцы-послушники (Acolyte Cultists)</t>
+          <t>Монстры (Monsters)</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>6 — база и все допы, константа</t>
+          <t>8–10 на фракцию — база и допы</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -3080,12 +3077,12 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/adept.png (арт-референс)</t>
+          <t>Templates/Units/Клонэйд Ресёрч/</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -3094,7 +3091,11 @@
         </is>
       </c>
       <c r="J50" s="5" t="n"/>
-      <c r="K50" s="3" t="inlineStr"/>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>робот «Стервятник» 2, танк «Чёрная смерть» 4, робот «Рипо» М-3 3</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -3104,22 +3105,22 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Клонэйд Ресёрч — боевые машины</t>
+          <t>Клонэйд Ресёрч — боевой робот «Жнец»</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Монстры (Monsters)</t>
+          <t>Великий Древний (Great Old One)</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>8–10 на фракцию — база и допы</t>
+          <t>1 — типовое; 2 у Yellow Sign (база), 3 у Daemon Sultan, 0 у The Ancients</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -3129,12 +3130,12 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/Клонэйд Ресёрч/</t>
+          <t>Иллюстрации/ (арт-референсы)</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -3143,11 +3144,7 @@
         </is>
       </c>
       <c r="J51" s="5" t="n"/>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>робот «Стервятник» 2, танк «Чёрная смерть» 4, робот «Рипо» М-3 3</t>
-        </is>
-      </c>
+      <c r="K51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -3157,12 +3154,12 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Клонэйд Ресёрч — боевой робот «Жнец»</t>
+          <t>Клонэйд Ресёрч — планшет фракции</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Великий Древний (Great Old One)</t>
+          <t>Планшет фракции (Faction Card)</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -3172,22 +3169,22 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>1 — типовое; 2 у Yellow Sign (база), 3 у Daemon Sultan, 0 у The Ancients</t>
+          <t>1 — база и каждый доп</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>док фракций v2.0</t>
+          <t>правила, §Компоненты</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>планшет, A4 landscape</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Иллюстрации/ (арт-референсы)</t>
+          <t>Templates/Saved/Faction Card — Клонэйд Ресёрч.pdf (2 стр.)</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -3206,22 +3203,22 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Клонэйд Ресёрч — планшет фракции</t>
+          <t>Клонэйд Ресёрч — карты целей (задач)</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Планшет фракции (Faction Card)</t>
+          <t>Требования к заклинаниям (Spellbook requirements) — слоты на планшете</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>1 — база и каждый доп</t>
+          <t>6 слотов на планшете — база и каждый доп</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -3231,12 +3228,12 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>планшет, A4 landscape</t>
+          <t>карта, Mini USA</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Faction Card — Клонэйд Ресёрч.pdf (2 стр.)</t>
+          <t>Templates/Saved/Технологии и задачи.pdf (48 карт целей на 8 фракций)</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -3245,7 +3242,11 @@
         </is>
       </c>
       <c r="J53" s="5" t="n"/>
-      <c r="K53" s="3" t="inlineStr"/>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW условия напечатаны прямо на планшете, отдельных карт нет.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -3255,12 +3256,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Клонэйд Ресёрч — карты целей (задач)</t>
+          <t>Клонэйд Ресёрч — карты технологий</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Требования к заклинаниям (Spellbook requirements) — слоты на планшете</t>
+          <t>Книги заклинаний (Spellbooks) — картонные жетоны-накладки</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -3270,7 +3271,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>6 слотов на планшете — база и каждый доп</t>
+          <t>6 на фракцию — база (24 на 4 фракции) и каждый доп</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -3285,7 +3286,7 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Технологии и задачи.pdf (48 карт целей на 8 фракций)</t>
+          <t>Templates/Saved/Технологии и задачи.pdf</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -3296,7 +3297,7 @@
       <c r="J54" s="5" t="n"/>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW условия напечатаны прямо на планшете, отдельных карт нет.</t>
+          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW это жетоны, которыми накрывают слоты планшета. Карта должна физически ложиться на слот. Расхождение дока: «Генетический эксперимент» / «Генетическая модификация».</t>
         </is>
       </c>
     </row>
@@ -3308,22 +3309,22 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Клонэйд Ресёрч — карты технологий</t>
+          <t>Клонэйд Ресёрч — маркер фракции</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Книги заклинаний (Spellbooks) — картонные жетоны-накладки</t>
+          <t>Маркеры фракции (Faction Markers): Doom + Power</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>6 на фракцию — база (24 на 4 фракции) и каждый доп</t>
+          <t>2 на фракцию — база</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -3333,12 +3334,12 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>карта, Mini USA</t>
+          <t>акрил, ⌀18 мм</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Технологии и задачи.pdf</t>
+          <t>Под Акрил/07. Жетоны-логотипы, шестигранные - по 1шт - ⌀18мм/Клонэйд Ресёрч.png</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
@@ -3349,7 +3350,7 @@
       <c r="J55" s="5" t="n"/>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW это жетоны, которыми накрывают слоты планшета. Карта должна физически ложиться на слот. Расхождение дока: «Генетический эксперимент» / «Генетическая модификация».</t>
+          <t>Вариант «плашка с гексом». Альтернатива «символ с обводкой» — Под Акрил/_Логотипы — варианты/.</t>
         </is>
       </c>
     </row>
@@ -3361,48 +3362,48 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Клонэйд Ресёрч — маркер фракции</t>
+          <t>Клонэйд Ресёрч — уникальные жетоны</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Маркеры фракции (Faction Markers): Doom + Power</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>2 на фракцию — база</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>правила, §Компоненты</t>
+          <t>док фракций v2.0</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>акрил, ⌀18 мм</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Под Акрил/07. Жетоны-логотипы, шестигранные - по 1шт - ⌀18мм/Клонэйд Ресёрч.png</t>
-        </is>
-      </c>
-      <c r="I56" s="7" t="inlineStr">
-        <is>
-          <t>готово</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J56" s="5" t="n"/>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>Вариант «плашка с гексом». Альтернатива «символ с обводкой» — Под Акрил/_Логотипы — варианты/.</t>
+          <t>Уникальных компонентов у фракции нет.</t>
         </is>
       </c>
     </row>
@@ -3414,12 +3415,12 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Клонэйд Ресёрч — уникальные жетоны</t>
+          <t>Moon Systems — пехотинцы «Рекрут»</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Пехотинцы-послушники (Acolyte Cultists)</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -3429,7 +3430,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6 — база и все допы, константа</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -3439,12 +3440,12 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Templates/Units/adept.png (арт-референс)</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -3455,7 +3456,7 @@
       <c r="J57" s="5" t="n"/>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>Уникальных компонентов у фракции нет.</t>
+          <t>Moon Systems — единственная фракция без пехотинцев; правила при этом утверждают «у каждой фракции 6 пехотинцев». См. «Расхождения».</t>
         </is>
       </c>
     </row>
@@ -3467,22 +3468,22 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Moon Systems — пехотинцы «Рекрут»</t>
+          <t>Moon Systems — боевые машины</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Пехотинцы-послушники (Acolyte Cultists)</t>
+          <t>Монстры (Monsters)</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>6 — база и все допы, константа</t>
+          <t>8–10 на фракцию — база и допы</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -3492,23 +3493,23 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/adept.png (арт-референс)</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Templates/Units/Moon Systems/</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J58" s="5" t="n"/>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>Moon Systems — единственная фракция без пехотинцев; правила при этом утверждают «у каждой фракции 6 пехотинцев». См. «Расхождения».</t>
+          <t>андроид 6, терминатор CP-1 «Гибсон» 2, терминатор Т-800 2, терминатор Т-1000 2</t>
         </is>
       </c>
     </row>
@@ -3520,22 +3521,22 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Moon Systems — боевые машины</t>
+          <t>Moon Systems — боевой робот «Буран»</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Монстры (Monsters)</t>
+          <t>Великий Древний (Great Old One)</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>8–10 на фракцию — база и допы</t>
+          <t>1 — типовое; 2 у Yellow Sign (база), 3 у Daemon Sultan, 0 у The Ancients</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -3545,12 +3546,12 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/Moon Systems/</t>
+          <t>Иллюстрации/ (арт-референсы)</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
@@ -3559,11 +3560,7 @@
         </is>
       </c>
       <c r="J59" s="5" t="n"/>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>андроид 6, терминатор CP-1 «Гибсон» 2, терминатор Т-800 2, терминатор Т-1000 2</t>
-        </is>
-      </c>
+      <c r="K59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -3573,12 +3570,12 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Moon Systems — боевой робот «Буран»</t>
+          <t>Moon Systems — планшет фракции</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Великий Древний (Great Old One)</t>
+          <t>Планшет фракции (Faction Card)</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -3588,22 +3585,22 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>1 — типовое; 2 у Yellow Sign (база), 3 у Daemon Sultan, 0 у The Ancients</t>
+          <t>1 — база и каждый доп</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>док фракций v2.0</t>
+          <t>правила, §Компоненты</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>планшет, A4 landscape</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Иллюстрации/ (арт-референсы)</t>
+          <t>Templates/Saved/Faction Card — Moon Systems.pdf (2 стр.)</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
@@ -3622,22 +3619,22 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Moon Systems — планшет фракции</t>
+          <t>Moon Systems — карты целей (задач)</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Планшет фракции (Faction Card)</t>
+          <t>Требования к заклинаниям (Spellbook requirements) — слоты на планшете</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>1 — база и каждый доп</t>
+          <t>6 слотов на планшете — база и каждый доп</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -3647,12 +3644,12 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>планшет, A4 landscape</t>
+          <t>карта, Mini USA</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Faction Card — Moon Systems.pdf (2 стр.)</t>
+          <t>Templates/Saved/Технологии и задачи.pdf (48 карт целей на 8 фракций)</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
@@ -3661,7 +3658,11 @@
         </is>
       </c>
       <c r="J61" s="5" t="n"/>
-      <c r="K61" s="3" t="inlineStr"/>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW условия напечатаны прямо на планшете, отдельных карт нет.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -3671,12 +3672,12 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Moon Systems — карты целей (задач)</t>
+          <t>Moon Systems — карты технологий</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Требования к заклинаниям (Spellbook requirements) — слоты на планшете</t>
+          <t>Книги заклинаний (Spellbooks) — картонные жетоны-накладки</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -3686,7 +3687,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>6 слотов на планшете — база и каждый доп</t>
+          <t>6 на фракцию — база (24 на 4 фракции) и каждый доп</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -3701,7 +3702,7 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Технологии и задачи.pdf (48 карт целей на 8 фракций)</t>
+          <t>Templates/Saved/Технологии и задачи.pdf</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
@@ -3712,7 +3713,7 @@
       <c r="J62" s="5" t="n"/>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW условия напечатаны прямо на планшете, отдельных карт нет.</t>
+          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW это жетоны, которыми накрывают слоты планшета. Карта должна физически ложиться на слот.</t>
         </is>
       </c>
     </row>
@@ -3724,22 +3725,22 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Moon Systems — карты технологий</t>
+          <t>Moon Systems — маркер фракции</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Книги заклинаний (Spellbooks) — картонные жетоны-накладки</t>
+          <t>Маркеры фракции (Faction Markers): Doom + Power</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>6 на фракцию — база (24 на 4 фракции) и каждый доп</t>
+          <t>2 на фракцию — база</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -3749,12 +3750,12 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>карта, Mini USA</t>
+          <t>акрил, ⌀18 мм</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Технологии и задачи.pdf</t>
+          <t>Под Акрил/07. Жетоны-логотипы, шестигранные - по 1шт - ⌀18мм/Moon Systems.png</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
@@ -3765,7 +3766,7 @@
       <c r="J63" s="5" t="n"/>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW это жетоны, которыми накрывают слоты планшета. Карта должна физически ложиться на слот.</t>
+          <t>Вариант «плашка с гексом». Альтернатива «символ с обводкой» — Под Акрил/_Логотипы — варианты/.</t>
         </is>
       </c>
     </row>
@@ -3777,12 +3778,12 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Moon Systems — маркер фракции</t>
+          <t>Moon Systems — Планшет (тайл) «Луна»</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Маркеры фракции (Faction Markers): Doom + Power</t>
+          <t>Аналог — тайл Луны у фракции Bubastis (Onslaught 4)</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -3792,7 +3793,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>2 на фракцию — база</t>
+          <t>1 — доп. CW-F8</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -3802,12 +3803,12 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>акрил, ⌀18 мм</t>
+          <t>картон</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Под Акрил/07. Жетоны-логотипы, шестигранные - по 1шт - ⌀18мм/Moon Systems.png</t>
+          <t>Templates/Saved/Moon.png (RGB 1254×1254)</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -3818,7 +3819,7 @@
       <c r="J64" s="5" t="n"/>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>Вариант «плашка с гексом». Альтернатива «символ с обводкой» — Под Акрил/_Логотипы — варианты/.</t>
+          <t>Утверждено (подтверждено Alek), оставляем как есть. Прежняя задача «перегенерировать в большем разрешении» снята.</t>
         </is>
       </c>
     </row>
@@ -3830,50 +3831,46 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Moon Systems — Планшет (тайл) «Луна»</t>
+          <t>Сайнтифик Солюшн — пехотинцы «Рекрут»</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Аналог — тайл Луны у фракции Bubastis (Onslaught 4)</t>
+          <t>Пехотинцы-послушники (Acolyte Cultists)</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>1 — доп. CW-F8</t>
+          <t>6 — база и все допы, константа</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>правила, §Компоненты</t>
+          <t>док фракций v2.0</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>картон</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Moon.png (RGB 1254×1254)</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>требует доработки</t>
+          <t>Templates/Units/adept.png (арт-референс)</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J65" s="5" t="n"/>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>Перегенерировать в большем разрешении.</t>
-        </is>
-      </c>
+      <c r="K65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -3883,22 +3880,22 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Сайнтифик Солюшн — пехотинцы «Рекрут»</t>
+          <t>Сайнтифик Солюшн — боевые машины</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Пехотинцы-послушники (Acolyte Cultists)</t>
+          <t>Монстры (Monsters)</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>6 — база и все допы, константа</t>
+          <t>8–10 на фракцию — база и допы</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -3908,12 +3905,12 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/adept.png (арт-референс)</t>
+          <t>Templates/Units/Сайнтифик Солюшн/</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
@@ -3922,7 +3919,11 @@
         </is>
       </c>
       <c r="J66" s="5" t="n"/>
-      <c r="K66" s="3" t="inlineStr"/>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>ББМ «Квант» 4, РСЗО «Вектор» 3, супертанк «Тесла-Танк» 2</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -3932,22 +3933,22 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Сайнтифик Солюшн — боевые машины</t>
+          <t>Сайнтифик Солюшн — боевой робот «Шрёдингер» (в PDF — «Шредингер»)</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Монстры (Monsters)</t>
+          <t>Великий Древний (Great Old One)</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>8–10 на фракцию — база и допы</t>
+          <t>1 — типовое; 2 у Yellow Sign (база), 3 у Daemon Sultan, 0 у The Ancients</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -3957,12 +3958,12 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/Сайнтифик Солюшн/</t>
+          <t>Иллюстрации/ (арт-референсы)</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
@@ -3973,7 +3974,7 @@
       <c r="J67" s="5" t="n"/>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>ББМ «Квант» 4, РСЗО «Вектор» 3, супертанк «Тесла-Танк» 2</t>
+          <t>Написание расходится: CLAUDE.md «Шрёдингер», карты «Шредингер».</t>
         </is>
       </c>
     </row>
@@ -3985,12 +3986,12 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Сайнтифик Солюшн — боевой робот «Шрёдингер» (в PDF — «Шредингер»)</t>
+          <t>Сайнтифик Солюшн — планшет фракции</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Великий Древний (Great Old One)</t>
+          <t>Планшет фракции (Faction Card)</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -4000,22 +4001,22 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>1 — типовое; 2 у Yellow Sign (база), 3 у Daemon Sultan, 0 у The Ancients</t>
+          <t>1 — база и каждый доп</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>док фракций v2.0</t>
+          <t>правила, §Компоненты</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>планшет, A4 landscape</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Иллюстрации/ (арт-референсы)</t>
+          <t>Templates/Saved/Faction Card — Сайнтифик Солюшн.pdf (2 стр.)</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
@@ -4024,11 +4025,7 @@
         </is>
       </c>
       <c r="J68" s="5" t="n"/>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>Написание расходится: CLAUDE.md «Шрёдингер», карты «Шредингер».</t>
-        </is>
-      </c>
+      <c r="K68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -4038,22 +4035,22 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Сайнтифик Солюшн — планшет фракции</t>
+          <t>Сайнтифик Солюшн — карты целей (задач)</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Планшет фракции (Faction Card)</t>
+          <t>Требования к заклинаниям (Spellbook requirements) — слоты на планшете</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>1 — база и каждый доп</t>
+          <t>6 слотов на планшете — база и каждый доп</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -4063,12 +4060,12 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>планшет, A4 landscape</t>
+          <t>карта, Mini USA</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Faction Card — Сайнтифик Солюшн.pdf (2 стр.)</t>
+          <t>Templates/Saved/Технологии и задачи.pdf (48 карт целей на 8 фракций)</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
@@ -4077,7 +4074,11 @@
         </is>
       </c>
       <c r="J69" s="5" t="n"/>
-      <c r="K69" s="3" t="inlineStr"/>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW условия напечатаны прямо на планшете, отдельных карт нет.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -4087,12 +4088,12 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Сайнтифик Солюшн — карты целей (задач)</t>
+          <t>Сайнтифик Солюшн — карты технологий</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Требования к заклинаниям (Spellbook requirements) — слоты на планшете</t>
+          <t>Книги заклинаний (Spellbooks) — картонные жетоны-накладки</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -4102,7 +4103,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>6 слотов на планшете — база и каждый доп</t>
+          <t>6 на фракцию — база (24 на 4 фракции) и каждый доп</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -4117,7 +4118,7 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Технологии и задачи.pdf (48 карт целей на 8 фракций)</t>
+          <t>Templates/Saved/Технологии и задачи.pdf</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
@@ -4128,7 +4129,7 @@
       <c r="J70" s="5" t="n"/>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW условия напечатаны прямо на планшете, отдельных карт нет.</t>
+          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW это жетоны, которыми накрывают слоты планшета. Карта должна физически ложиться на слот.</t>
         </is>
       </c>
     </row>
@@ -4140,22 +4141,22 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Сайнтифик Солюшн — карты технологий</t>
+          <t>Сайнтифик Солюшн — маркер фракции</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Книги заклинаний (Spellbooks) — картонные жетоны-накладки</t>
+          <t>Маркеры фракции (Faction Markers): Doom + Power</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>6 на фракцию — база (24 на 4 фракции) и каждый доп</t>
+          <t>2 на фракцию — база</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -4165,12 +4166,12 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>карта, Mini USA</t>
+          <t>акрил, ⌀18 мм</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Технологии и задачи.pdf</t>
+          <t>Под Акрил/07. Жетоны-логотипы, шестигранные - по 1шт - ⌀18мм/Сайнтифик Солюшн.png</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
@@ -4181,7 +4182,7 @@
       <c r="J71" s="5" t="n"/>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW это жетоны, которыми накрывают слоты планшета. Карта должна физически ложиться на слот.</t>
+          <t>Вариант «плашка с гексом». Альтернатива «символ с обводкой» — Под Акрил/_Логотипы — варианты/.</t>
         </is>
       </c>
     </row>
@@ -4193,48 +4194,48 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Сайнтифик Солюшн — маркер фракции</t>
+          <t>Сайнтифик Солюшн — уникальные жетоны</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Маркеры фракции (Faction Markers): Doom + Power</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>2 на фракцию — база</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>правила, §Компоненты</t>
+          <t>док фракций v2.0</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>акрил, ⌀18 мм</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>Под Акрил/07. Жетоны-логотипы, шестигранные - по 1шт - ⌀18мм/Сайнтифик Солюшн.png</t>
-        </is>
-      </c>
-      <c r="I72" s="7" t="inlineStr">
-        <is>
-          <t>готово</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J72" s="5" t="n"/>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>Вариант «плашка с гексом». Альтернатива «символ с обводкой» — Под Акрил/_Логотипы — варианты/.</t>
+          <t>Уникальных компонентов у фракции нет.</t>
         </is>
       </c>
     </row>
@@ -4246,22 +4247,22 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Сайнтифик Солюшн — уникальные жетоны</t>
+          <t>Североамериканский Альянс — пехотинцы «Рекрут»</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Пехотинцы-послушники (Acolyte Cultists)</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6 — база и все допы, константа</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -4271,25 +4272,21 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Templates/Units/adept.png (арт-референс)</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J73" s="5" t="n"/>
-      <c r="K73" s="3" t="inlineStr">
-        <is>
-          <t>Уникальных компонентов у фракции нет.</t>
-        </is>
-      </c>
+      <c r="K73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -4299,22 +4296,22 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Североамериканский Альянс — пехотинцы «Рекрут»</t>
+          <t>Североамериканский Альянс — боевые машины</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Пехотинцы-послушники (Acolyte Cultists)</t>
+          <t>Монстры (Monsters)</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>≥5 (полный список неизвестен)</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>6 — база и все допы, константа</t>
+          <t>8–10 на фракцию — база и допы</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -4324,12 +4321,12 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/adept.png (арт-референс)</t>
+          <t>Templates/Units/Североамериканский Альянс/</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
@@ -4338,7 +4335,11 @@
         </is>
       </c>
       <c r="J74" s="5" t="n"/>
-      <c r="K74" s="3" t="inlineStr"/>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>БРМ «Визард» 2, БРМ «Снейк» 3, далее экспорт обрывается — экспорт дока обрывается, 3-я и далее БМ на бумаге неизвестны. Миниатюры при этом закуплены и покрашены по всем 8 фракциям (подтверждено Alek) — восстановить состав можно по ним.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -4348,22 +4349,22 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Североамериканский Альянс — боевые машины</t>
+          <t>Североамериканский Альянс — боевой робот «Тексан» (в PDF карт и в Иллюстрациях — «Техасец»)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Монстры (Monsters)</t>
+          <t>Великий Древний (Great Old One)</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>≥5 (полный список неизвестен)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>8–10 на фракцию — база и допы</t>
+          <t>1 — типовое; 2 у Yellow Sign (база), 3 у Daemon Sultan, 0 у The Ancients</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -4373,23 +4374,23 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/Североамериканский Альянс/</t>
-        </is>
-      </c>
-      <c r="I75" s="4" t="inlineStr">
-        <is>
-          <t>требует доработки</t>
+          <t>Иллюстрации/ (арт-референсы)</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J75" s="5" t="n"/>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>БРМ «Визард» 2, БРМ «Снейк» 3, далее экспорт обрывается — экспорт дока обрывается, 3-я и далее БМ неизвестны</t>
+          <t>Название расходится: CLAUDE.md «Тексан», карты и иллюстрация «Техасец». Характеристики в экспорте дока отсутствуют.</t>
         </is>
       </c>
     </row>
@@ -4401,12 +4402,12 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Североамериканский Альянс — боевой робот «Тексан» (в PDF карт и в Иллюстрациях — «Техасец»)</t>
+          <t>Североамериканский Альянс — планшет фракции</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Великий Древний (Great Old One)</t>
+          <t>Планшет фракции (Faction Card)</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -4416,22 +4417,22 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>1 — типовое; 2 у Yellow Sign (база), 3 у Daemon Sultan, 0 у The Ancients</t>
+          <t>1 — база и каждый доп</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>док фракций v2.0</t>
+          <t>правила, §Компоненты</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>планшет, A4 landscape</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>Иллюстрации/ (арт-референсы)</t>
+          <t>Templates/Saved/Faction Card — Североамериканский Альянс.pdf (2 стр.)</t>
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr">
@@ -4440,11 +4441,7 @@
         </is>
       </c>
       <c r="J76" s="5" t="n"/>
-      <c r="K76" s="3" t="inlineStr">
-        <is>
-          <t>Название расходится: CLAUDE.md «Тексан», карты и иллюстрация «Техасец». Характеристики в экспорте дока отсутствуют.</t>
-        </is>
-      </c>
+      <c r="K76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -4454,22 +4451,22 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Североамериканский Альянс — планшет фракции</t>
+          <t>Североамериканский Альянс — карты целей (задач)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Планшет фракции (Faction Card)</t>
+          <t>Требования к заклинаниям (Spellbook requirements) — слоты на планшете</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>1 — база и каждый доп</t>
+          <t>6 слотов на планшете — база и каждый доп</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -4479,12 +4476,12 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>планшет, A4 landscape</t>
+          <t>карта, Mini USA</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Faction Card — Североамериканский Альянс.pdf (2 стр.)</t>
+          <t>Templates/Saved/Технологии и задачи.pdf (48 карт целей на 8 фракций)</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
@@ -4493,7 +4490,11 @@
         </is>
       </c>
       <c r="J77" s="5" t="n"/>
-      <c r="K77" s="3" t="inlineStr"/>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW условия напечатаны прямо на планшете, отдельных карт нет.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -4503,12 +4504,12 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Североамериканский Альянс — карты целей (задач)</t>
+          <t>Североамериканский Альянс — карты технологий</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Требования к заклинаниям (Spellbook requirements) — слоты на планшете</t>
+          <t>Книги заклинаний (Spellbooks) — картонные жетоны-накладки</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -4518,7 +4519,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>6 слотов на планшете — база и каждый доп</t>
+          <t>6 на фракцию — база (24 на 4 фракции) и каждый доп</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -4533,7 +4534,7 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Технологии и задачи.pdf (48 карт целей на 8 фракций)</t>
+          <t>Templates/Saved/Технологии и задачи.pdf</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
@@ -4544,7 +4545,7 @@
       <c r="J78" s="5" t="n"/>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW условия напечатаны прямо на планшете, отдельных карт нет.</t>
+          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW это жетоны, которыми накрывают слоты планшета. Карта должна физически ложиться на слот. 6-я технология в карте названа «Специальная операция», в оглавлении дока — «Специальный договор».</t>
         </is>
       </c>
     </row>
@@ -4556,22 +4557,22 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Североамериканский Альянс — карты технологий</t>
+          <t>Североамериканский Альянс — маркер фракции</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Книги заклинаний (Spellbooks) — картонные жетоны-накладки</t>
+          <t>Маркеры фракции (Faction Markers): Doom + Power</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>6 на фракцию — база (24 на 4 фракции) и каждый доп</t>
+          <t>2 на фракцию — база</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -4581,12 +4582,12 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>карта, Mini USA</t>
+          <t>акрил, ⌀18 мм</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Технологии и задачи.pdf</t>
+          <t>Под Акрил/07. Жетоны-логотипы, шестигранные - по 1шт - ⌀18мм/Североамериканский Альянс.png</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
@@ -4597,7 +4598,7 @@
       <c r="J79" s="5" t="n"/>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА по носителю: в CW это жетоны, которыми накрывают слоты планшета. Карта должна физически ложиться на слот. 6-я технология в карте названа «Специальная операция», в оглавлении дока — «Специальный договор».</t>
+          <t>Вариант «плашка с гексом». Альтернатива «символ с обводкой» — Под Акрил/_Логотипы — варианты/.</t>
         </is>
       </c>
     </row>
@@ -4609,120 +4610,120 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Североамериканский Альянс — маркер фракции</t>
+          <t>Североамериканский Альянс — уникальные жетоны</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Маркеры фракции (Faction Markers): Doom + Power</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>2 на фракцию — база</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>правила, §Компоненты</t>
+          <t>док фракций v2.0</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>акрил, ⌀18 мм</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>Под Акрил/07. Жетоны-логотипы, шестигранные - по 1шт - ⌀18мм/Североамериканский Альянс.png</t>
-        </is>
-      </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>готово</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J80" s="5" t="n"/>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>Вариант «плашка с гексом». Альтернатива «символ с обводкой» — Под Акрил/_Логотипы — варианты/.</t>
+          <t>Уникальных компонентов у фракции нет.</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>2. Компоненты фракции</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>Североамериканский Альянс — уникальные жетоны</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>док фракций v2.0</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J81" s="5" t="n"/>
-      <c r="K81" s="3" t="inlineStr">
-        <is>
-          <t>Уникальных компонентов у фракции нет.</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>3. Варианты игры</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n"/>
+      <c r="E81" s="2" t="n"/>
+      <c r="F81" s="2" t="n"/>
+      <c r="G81" s="2" t="n"/>
+      <c r="H81" s="2" t="n"/>
+      <c r="I81" s="2" t="n"/>
+      <c r="J81" s="2" t="n"/>
+      <c r="K81" s="2" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>3. Варианты игры</t>
         </is>
       </c>
-      <c r="B82" s="2" t="n"/>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n"/>
-      <c r="E82" s="2" t="n"/>
-      <c r="F82" s="2" t="n"/>
-      <c r="G82" s="2" t="n"/>
-      <c r="H82" s="2" t="n"/>
-      <c r="I82" s="2" t="n"/>
-      <c r="J82" s="2" t="n"/>
-      <c r="K82" s="2" t="n"/>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Особые военные фабрики</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Colour Out of Space Gate Pack (CW-U7) — 8 врат в цветах фракций; Eldritch Gate Pack (CW-U9) — 22 врат</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>8 — доп. Onslaught 2</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>правила, §Дополнительные компоненты</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>картон</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>Templates/Saved/Factory Tokens v2.pdf, стр. 2 (S-01…S-10)</t>
+        </is>
+      </c>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="n"/>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>10 фабрик S-01…S-10, каждая со своим символом. Символы совпадают с таблицами карт событий. В CW эффекты особых врат разыгрываются броском кубика, а не картами.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -4732,37 +4733,37 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Особые военные фабрики</t>
+          <t>Карты событий фабрик</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Colour Out of Space Gate Pack (CW-U7) — 8 врат в цветах фракций; Eldritch Gate Pack (CW-U9) — 22 врат</t>
+          <t>Официальных карт событий в Cthulhu Wars нет (только фанатские варианты на BGG)</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6 рабочих (напечатано 8)</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>8 — доп. Onslaught 2</t>
+          <t>нет в оригинале</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>правила, §Дополнительные компоненты</t>
+          <t>правила + файл</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>картон</t>
+          <t>карта</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Factory Tokens v2.pdf, стр. 2 (S-01…S-10)</t>
+          <t>Templates/Saved/Factory Events.pdf (3 стр.)</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
@@ -4773,7 +4774,7 @@
       <c r="J83" s="5" t="n"/>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>10 фабрик S-01…S-10, каждая со своим символом. Символы совпадают с таблицами карт событий. В CW эффекты особых врат разыгрываются броском кубика, а не картами.</t>
+          <t>СВЕРХ ОРИГИНАЛА. Напечатаны. В PDF 8 карт: ПРОФИЦИТ, ВОЛАТИЛЬНОСТЬ РЫНКОВ, ДЕСТАБИЛИЗАЦИЯ БИРЖИ, СБОЙ ПОСТАВОК, ПЕРЕПРОФИЛИРОВАНИЕ, РЕСТРУКТУРИЗАЦИЯ, СБОЙ ×2 — две из них эксперимент и в рабочую колоду не входят (подтверждено Alek).</t>
         </is>
       </c>
     </row>
@@ -4785,48 +4786,48 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Карты событий фабрик</t>
+          <t>Фигурки полковников</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Официальных карт событий в Cthulhu Wars нет (только фанатские варианты на BGG)</t>
+          <t>Верховные жрецы (High Priests, CW-U3) — 9 фигур, по 1 на фракцию</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>6 (правила) / 8 (в PDF)</t>
+          <t>по 1 на фракцию = 8</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>нет в оригинале</t>
+          <t>9 — доп. Onslaught 1</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>правила + файл</t>
+          <t>правила, §Дополнительные компоненты</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>карта</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Factory Events.pdf (3 стр.)</t>
-        </is>
-      </c>
-      <c r="I84" s="4" t="inlineStr">
-        <is>
-          <t>требует доработки</t>
+          <t>Templates/Units/colonel.png (арт-референс)</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J84" s="5" t="n"/>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА. В PDF 8 карт: ПРОФИЦИТ, ВОЛАТИЛЬНОСТЬ РЫНКОВ, ДЕСТАБИЛИЗАЦИЯ БИРЖИ, СБОЙ ПОСТАВОК, ПЕРЕПРОФИЛИРОВАНИЕ, РЕСТРУКТУРИЗАЦИЯ, СБОЙ ×2. Правила говорят 6.</t>
+          <t>Полковник — пехотинец стоимостью 3, способность «Боевое донесение» одинакова у всех фракций. В таблице отрядов Moon Systems полковник отсутствует.</t>
         </is>
       </c>
     </row>
@@ -4838,37 +4839,37 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Фигурки полковников</t>
+          <t>Карты уникальных полковников</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Верховные жрецы (High Priests, CW-U3) — 9 фигур, по 1 на фракцию</t>
+          <t>Investigators (8 шт.) + The Eidolon + The Prophetess — Onslaught 3 Stretch Goal Box</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>по 1 на фракцию = 8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>9 — доп. Onslaught 1</t>
+          <t>8 + 2 — доп. Onslaught 3</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>правила, §Дополнительные компоненты</t>
+          <t>правила + файл (подтверждено: 11 карт)</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>миниатюра (закуплена)</t>
+          <t>карта</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/colonel.png (арт-референс)</t>
+          <t>Templates/Saved/Уникальные полковники.pdf (4 стр., 11 карт)</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
@@ -4879,7 +4880,7 @@
       <c r="J85" s="5" t="n"/>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>Полковник — пехотинец стоимостью 3, способность «Боевое донесение» одинакова у всех фракций. В таблице отрядов Moon Systems полковник отсутствует.</t>
+          <t>Подтверждено 11 карт: Герберт Морроу, Сигэру Исии, Амелия Кейн, Кассия Рэйвен, Бато Распутин, Эвелин Тайрелл, Джон Крамер, Роберт Клоуз, Виктор «Шайн» Ковач, Ной Гарднер, Генри Брут. В CW Investigators вручаются противнику как обременение — у нас берутся себе.</t>
         </is>
       </c>
     </row>
@@ -4891,48 +4892,48 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Карты уникальных полковников</t>
+          <t>Наёмники: боевые машины (карты лояльности + фигурки)</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Investigators (8 шт.) + The Eidolon + The Prophetess — Onslaught 3 Stretch Goal Box</t>
+          <t>Нейтральные монстры (Neutral Monsters): Azathoth CW-F4 — 12 фигур; Dreamlands Surface — 9; Dreamlands Underworld — 9</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>количество не задано</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>8 + 2 — доп. Onslaught 3</t>
+          <t>12 / 9 / 9 — доп. Onslaught 1</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>правила + файл (подтверждено: 11 карт)</t>
+          <t>правила (количество отсутствует)</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>карта</t>
+          <t>карта + миниатюра</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Уникальные полковники.pdf (4 стр., 11 карт)</t>
-        </is>
-      </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>готово</t>
+          <t>Drafts/Нефтяные войны (наемники).pdf (11 стр.)</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>не сделано</t>
         </is>
       </c>
       <c r="J86" s="5" t="n"/>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>Подтверждено 11 карт: Герберт Морроу, Сигэру Исии, Амелия Кейн, Кассия Рэйвен, Бато Распутин, Эвелин Тайрелл, Джон Крамер, Роберт Клоуз, Виктор «Шайн» Ковач, Ной Гарднер, Генри Брут. В CW Investigators вручаются противнику как обременение — у нас берутся себе.</t>
+          <t>Правила описывают механику (карта лояльности за 2 влияния, не более 1 за раз), но количества не задают. Требуется решение.</t>
         </is>
       </c>
     </row>
@@ -4944,12 +4945,12 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Наёмники: боевые машины (карты лояльности + фигурки)</t>
+          <t>Наёмники: мехи (карты лояльности + фигурки)</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Нейтральные монстры (Neutral Monsters): Azathoth CW-F4 — 12 фигур; Dreamlands Surface — 9; Dreamlands Underworld — 9</t>
+          <t>Cosmic Terrors Pack (CW-U5) — 3 шт. + 3 карты лояльности; позже Brown Jenkin, Cacodemon</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -4959,7 +4960,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>12 / 9 / 9 — доп. Onslaught 1</t>
+          <t>3 — доп. Onslaught 2</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -4974,7 +4975,7 @@
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>Drafts/Нефтяные войны (наемники).pdf (11 стр.)</t>
+          <t>Drafts/Нефтяные войны (наемники).pdf</t>
         </is>
       </c>
       <c r="I87" s="6" t="inlineStr">
@@ -4985,7 +4986,7 @@
       <c r="J87" s="5" t="n"/>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>Правила описывают механику (карта лояльности за 2 влияния, не более 1 за раз), но количества не задают. Требуется решение.</t>
+          <t>Стоимость 2 нефти + 2 влияния, не более 1 карты в фазу влияния. Количество не задано.</t>
         </is>
       </c>
     </row>
@@ -4997,12 +4998,12 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Наёмники: мехи (карты лояльности + фигурки)</t>
+          <t>Наёмники: боевые роботы (карты лояльности + фигурки + технологии)</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Cosmic Terrors Pack (CW-U5) — 3 шт. + 3 карты лояльности; позже Brown Jenkin, Cacodemon</t>
+          <t>Независимые Великие Древние (Independent Great Old Ones) — GOO Pack 1–4, Azathoth, Ramsey Campbell 1–2, Masks of Nyarlathotep и др.</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -5012,7 +5013,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>3 — доп. Onslaught 2</t>
+          <t>≈24–26 суммарно по всем допам (единого официального числа нет)</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -5038,7 +5039,7 @@
       <c r="J88" s="5" t="n"/>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>Стоимость 2 нефти + 2 влияния, не более 1 карты в фазу влияния. Количество не задано.</t>
+          <t>У каждого независимого — своя карта лояльности и свой спеллбук. Рекомендация правил: в первой партии на одного меньше числа игроков (калька с CW).</t>
         </is>
       </c>
     </row>
@@ -5050,48 +5051,48 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Наёмники: боевые роботы (карты лояльности + фигурки + технологии)</t>
+          <t>Лаборатория (жетон)</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Независимые Великие Древние (Independent Great Old Ones) — GOO Pack 1–4, Azathoth, Ramsey Campbell 1–2, Masks of Nyarlathotep и др.</t>
+          <t>Область Laboratory на карте Yuggoth (CW-M3) + переносной жетон Лаборатории</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>количество не задано</t>
+          <t>1 (выведено)</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>≈24–26 суммарно по всем допам (единого официального числа нет)</t>
+          <t>1 — доп. Onslaught 1</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>правила (количество отсутствует)</t>
+          <t>выведено (в правилах количество отсутствует)</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>карта + миниатюра</t>
+          <t>акрил, стенд ↔45 мм</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>Drafts/Нефтяные войны (наемники).pdf</t>
-        </is>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>не сделано</t>
+          <t>Под Акрил/02. Лаборатория - стенд - 1шт - ↔️45мм.png</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J89" s="5" t="n"/>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>У каждого независимого — своя карта лояльности и свой спеллбук. Рекомендация правил: в первой партии на одного меньше числа игроков (калька с CW).</t>
+          <t>Прямой аналог: в CW контроль врат в Лаборатории даёт действие «Хирургия» — уничтожить до 4 своих культистов и заменить Brain Cylinders. У нас — «Извлечение сознания», до 4 пехотинцев.</t>
         </is>
       </c>
     </row>
@@ -5103,37 +5104,37 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Лаборатория (жетон)</t>
+          <t>Энграммы</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Область Laboratory на карте Yuggoth (CW-M3) + переносной жетон Лаборатории</t>
+          <t>Мозговые цилиндры (Brain Cylinders) — по 4 на фракцию</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>1 (выведено)</t>
+          <t>8×4 = 32 (по файлу)</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>1 — доп. Onslaught 1</t>
+          <t>4 на фракцию — доп. Onslaught 1 (Yuggoth Map)</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>выведено (в правилах количество отсутствует)</t>
+          <t>файл в папке (в правилах количество отсутствует)</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>акрил, стенд ↔45 мм</t>
+          <t>акрил, ↕20 мм</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>Под Акрил/02. Лаборатория - стенд - 1шт - ↔️45мм.png</t>
+          <t>Под Акрил/03. Энграммы - 8x4шт - ↕️20мм.png</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
@@ -5144,7 +5145,7 @@
       <c r="J90" s="5" t="n"/>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>Прямой аналог: в CW контроль врат в Лаборатории даёт действие «Хирургия» — уничтожить до 4 своих культистов и заменить Brain Cylinders. У нас — «Извлечение сознания», до 4 пехотинцев.</t>
+          <t>Совпадает с CW: 4 на фракцию. Правила количество не задают, в действии — «до 4». Также используется картой уникального полковника Генри Брута.</t>
         </is>
       </c>
     </row>
@@ -5156,37 +5157,37 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Энграммы</t>
+          <t>ЦУ / Узел управления (жетон)</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Мозговые цилиндры (Brain Cylinders) — по 4 на фракцию</t>
+          <t>Slime Sea Overlook на карте Yuggoth — врата, дающие контроль над Слизнями</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>8×4 = 32 (по файлу)</t>
+          <t>1 (выведено)</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>4 на фракцию — доп. Onslaught 1 (Yuggoth Map)</t>
+          <t>1 — доп. Onslaught 1</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>файл в папке (в правилах количество отсутствует)</t>
+          <t>выведено (в правилах количество отсутствует)</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>акрил, ↕20 мм</t>
+          <t>акрил, стенд ↔45 мм</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>Под Акрил/03. Энграммы - 8x4шт - ↕️20мм.png</t>
+          <t>Под Акрил/05. ЦУ - стенд - 1шт - ↔️45мм.png</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr">
@@ -5197,7 +5198,7 @@
       <c r="J91" s="5" t="n"/>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>Совпадает с CW: 4 на фракцию. Правила количество не задают, в действии — «до 4». Также используется картой уникального полковника Генри Брута.</t>
+          <t>Ставится в регион с ≥3 соседними регионами. Даёт карту Контроля сети.</t>
         </is>
       </c>
     </row>
@@ -5209,37 +5210,37 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>ЦУ / Узел управления (жетон)</t>
+          <t>Зоны сети (жетоны)</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Slime Sea Overlook на карте Yuggoth — врата, дающие контроль над Слизнями</t>
+          <t>Прямого аналога нет; ближайшее — область Slime Sea на Yuggoth</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>1 (выведено)</t>
+          <t>3–4</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>1 — доп. Onslaught 1</t>
+          <t>нет прямого аналога</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>выведено (в правилах количество отсутствует)</t>
+          <t>правила, §Варианты → Рой боевых дронов</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>акрил, стенд ↔45 мм</t>
+          <t>акрил, ⌀20 мм</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>Под Акрил/05. ЦУ - стенд - 1шт - ↔️45мм.png</t>
+          <t>Под Акрил/06. Контроль - круглый жетон - ⌀20мм.png</t>
         </is>
       </c>
       <c r="I92" s="7" t="inlineStr">
@@ -5250,7 +5251,7 @@
       <c r="J92" s="5" t="n"/>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>Ставится в регион с ≥3 соседними регионами. Даёт карту Контроля сети.</t>
+          <t>СВЕРХ ОРИГИНАЛА. Арт сгенерирован, готовится к печати (подтверждено Alek). Файл назван «Контроль», хотя по роли это зоны сети для ЦУ — переименовать и дописать количество по конвенции §5 CLAUDE.md. Отдельного жетона контроля фабрик у нас нет: контроль обозначается пехотинцем поверх фабрики, как в CW.</t>
         </is>
       </c>
     </row>
@@ -5262,32 +5263,32 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Зоны сети (жетоны)</t>
+          <t>Карта «Контроль сети»</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Прямого аналога нет; ближайшее — область Slime Sea на Yuggoth</t>
+          <t>Карта лояльности Слизней (Slime Mold Loyalty Card)</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>3–4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>нет прямого аналога</t>
+          <t>1 — доп. Onslaught 1</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>правила, §Варианты → Рой боевых дронов</t>
+          <t>правила, §Варианты</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>акрил</t>
+          <t>карта</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
@@ -5303,7 +5304,7 @@
       <c r="J93" s="5" t="n"/>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА. Отдельного арта нет. Кандидат — «06. Контроль», но он сюжетно дублирует ЦУ; по решению перерисовать как локальный ретранслятор.</t>
+          <t>Механика 1-в-1: при смене владельца ключевых врат все Слизни/Рой мгновенно меняют хозяина.</t>
         </is>
       </c>
     </row>
@@ -5315,32 +5316,32 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Карта «Контроль сети»</t>
+          <t>Фигурки Роя боевых дронов</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Карта лояльности Слизней (Slime Mold Loyalty Card)</t>
+          <t>Слизни (Slime Molds) — 6 шт. (Yuggoth Map); также Filth Абхота — 12 жетонов</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>количество не задано</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>1 — доп. Onslaught 1</t>
+          <t>6 — доп. Onslaught 1</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>правила, §Варианты</t>
+          <t>правила (количество отсутствует)</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>карта</t>
+          <t>миниатюра</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
@@ -5356,7 +5357,7 @@
       <c r="J94" s="5" t="n"/>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>Механика 1-в-1: при смене владельца ключевых врат все Слизни/Рой мгновенно меняют хозяина.</t>
+          <t>Стоимость 0 если Роя нет в игре, иначе 1 — та же логика, что у Слизней в CW.</t>
         </is>
       </c>
     </row>
@@ -5368,48 +5369,48 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Фигурки Роя боевых дронов</t>
+          <t>Баланс сил</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Слизни (Slime Molds) — 6 шт. (Yuggoth Map); также Filth Абхота — 12 жетонов</t>
+          <t>Handicap Acolyte — официальные опциональные правила CW; Homebrew Faction (CW-U8), 9 серых акольтов (Onslaught 3)</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>количество не задано</t>
+          <t>±1 пехотинец (5 или 7)</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>6 — доп. Onslaught 1</t>
+          <t>±1 акольт (5 или 7) — доп. Onslaught 2/3</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>правила (количество отсутствует)</t>
+          <t>правила, §Варианты</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>миниатюра</t>
+          <t>миниатюра (закуплена, покрашена)</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>не сделано</t>
+          <t>отдельного компонента не требует</t>
+        </is>
+      </c>
+      <c r="I95" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J95" s="5" t="n"/>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>Стоимость 0 если Роя нет в игре, иначе 1 — та же логика, что у Слизней в CW.</t>
+          <t>НОВЫХ КОМПОНЕНТОВ НЕ ТРЕБУЕТ. По тексту правил рекрут берётся «из любой неиспользуемой в данной игре фракции» — то есть из уже закупленных миниатюр. В CW для этого сделали 9 отдельных серых акольтов, у нас гандикапный рекрут отличается цветом фракции. Открытый вопрос по правилам, не по компонентам: для сильного игрока сказано, что такой рекрут при уходе в запас убирается в коробку навсегда, а про 7-го рекрута слабого игрока правила молчат.</t>
         </is>
       </c>
     </row>
@@ -5421,22 +5422,22 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Баланс сил</t>
+          <t>Игра для двух игроков / эпическая игра</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Handicap Acolyte — официальные опциональные правила CW; Homebrew Faction (CW-U8), 9 серых акольтов (Onslaught 3)</t>
+          <t>Правила на 2 игроков (варианты CW)</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>±1 пехотинец (5 или 7)</t>
+          <t>доп. компонентов нет</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>±1 акольт (5 или 7) — доп. Onslaught 2/3</t>
+          <t>доп. компонентов нет</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -5446,7 +5447,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>миниатюра</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
@@ -5454,87 +5455,87 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I96" s="6" t="inlineStr">
-        <is>
-          <t>не сделано</t>
+      <c r="I96" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J96" s="5" t="n"/>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>Механика совпадает с CW дословно. У нас рекрут берётся из неиспользуемых фракций — отдельного компонента не требуется.</t>
+          <t>Требуют поле и трек Судного дня на 4 (обычная) и на 6 (эпическая) игроков.</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>3. Варианты игры</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>Игра для двух игроков / эпическая игра</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>Правила на 2 игроков (варианты CW)</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>доп. компонентов нет</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>доп. компонентов нет</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>правила, §Варианты</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I97" s="7" t="inlineStr">
-        <is>
-          <t>готово</t>
-        </is>
-      </c>
-      <c r="J97" s="5" t="n"/>
-      <c r="K97" s="3" t="inlineStr">
-        <is>
-          <t>Требуют поле и трек Судного дня на 4 (обычная) и на 6 (эпическая) игроков.</t>
-        </is>
-      </c>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>4. Сверх оригинала</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n"/>
+      <c r="E97" s="2" t="n"/>
+      <c r="F97" s="2" t="n"/>
+      <c r="G97" s="2" t="n"/>
+      <c r="H97" s="2" t="n"/>
+      <c r="I97" s="2" t="n"/>
+      <c r="J97" s="2" t="n"/>
+      <c r="K97" s="2" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>4. Сверх оригинала</t>
         </is>
       </c>
-      <c r="B98" s="2" t="n"/>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n"/>
-      <c r="E98" s="2" t="n"/>
-      <c r="F98" s="2" t="n"/>
-      <c r="G98" s="2" t="n"/>
-      <c r="H98" s="2" t="n"/>
-      <c r="I98" s="2" t="n"/>
-      <c r="J98" s="2" t="n"/>
-      <c r="K98" s="2" t="n"/>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Карты технологий как карты</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>В CW — картонные жетоны-накладки (Spellbooks)</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>8×6 = 48</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>24 жетона — база</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>правила + файл</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>карта, Mini USA</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>Templates/Saved/Технологии и задачи.pdf</t>
+        </is>
+      </c>
+      <c r="I98" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="n"/>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>СВЕРХ ОРИГИНАЛА (носитель). Карта должна физически ложиться на слот планшета.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -5544,12 +5545,12 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Карты технологий как карты</t>
+          <t>Карты целей как карты</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>В CW — картонные жетоны-накладки (Spellbooks)</t>
+          <t>В CW условия напечатаны на планшете, компонента нет</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -5559,7 +5560,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>24 жетона — база</t>
+          <t>0 (нет компонента)</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -5585,7 +5586,7 @@
       <c r="J99" s="5" t="n"/>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА (носитель). Карта должна физически ложиться на слот планшета.</t>
+          <t>СВЕРХ ОРИГИНАЛА. Подтверждено в PDF: 48 карт целей.</t>
         </is>
       </c>
     </row>
@@ -5597,22 +5598,22 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Карты целей как карты</t>
+          <t>Карты скрытого влияния как карты</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>В CW условия напечатаны на планшете, компонента нет</t>
+          <t>В CW — жетоны, тянутся из мешочка вслепую</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>8×6 = 48</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>0 (нет компонента)</t>
+          <t>36 жетонов — база</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -5627,7 +5628,7 @@
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Технологии и задачи.pdf</t>
+          <t>Templates/Saved/Карты скрытого влияния - (формат Mini USA).pdf</t>
         </is>
       </c>
       <c r="I100" s="7" t="inlineStr">
@@ -5638,7 +5639,7 @@
       <c r="J100" s="5" t="n"/>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА. Подтверждено в PDF: 48 карт целей.</t>
+          <t>СВЕРХ ОРИГИНАЛА (носитель). Числа 18/12/6 совпадают с CW; 4 лишние карты на листе — запас под брак резки и печати.</t>
         </is>
       </c>
     </row>
@@ -5650,22 +5651,22 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Карты скрытого влияния как карты</t>
+          <t>Карты событий фабрик</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>В CW — жетоны, тянутся из мешочка вслепую</t>
+          <t>Официальных карт событий в CW нет</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6 рабочих (напечатано 8)</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>36 жетонов — база</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -5675,23 +5676,23 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>карта, Mini USA</t>
+          <t>карта</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Карты скрытого влияния - (формат Mini USA).pdf</t>
-        </is>
-      </c>
-      <c r="I101" s="4" t="inlineStr">
-        <is>
-          <t>требует доработки</t>
+          <t>Templates/Saved/Factory Events.pdf</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J101" s="5" t="n"/>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА (носитель). Числа 18/12/6 совпадают с CW, но в PDF напечатано 40 карт.</t>
+          <t>СВЕРХ ОРИГИНАЛА. В CW эффекты особых врат разыгрываются броском кубика, а не картами.</t>
         </is>
       </c>
     </row>
@@ -5703,17 +5704,17 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Карты событий фабрик</t>
+          <t>Мех как отдельный тип отряда</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Официальных карт событий в CW нет</t>
+          <t>В CW нет; ближайшее — класс Terror (CW-U5)</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>6 / 8</t>
+          <t>3 (Братство Сингулярности)</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
@@ -5723,28 +5724,28 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>правила + файл</t>
+          <t>док фракций v2.0</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>карта</t>
+          <t>миниатюра</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Factory Events.pdf</t>
-        </is>
-      </c>
-      <c r="I102" s="4" t="inlineStr">
-        <is>
-          <t>требует доработки</t>
+          <t>Templates/Units/Братство Сингулярности/</t>
+        </is>
+      </c>
+      <c r="I102" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J102" s="5" t="n"/>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА. В CW эффекты особых врат разыгрываются броском кубика.</t>
+          <t>СВЕРХ ОРИГИНАЛА. Строится как боевая машина, но неуязвим к эффектам против БМ.</t>
         </is>
       </c>
     </row>
@@ -5756,22 +5757,22 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Жетон «Контроль»</t>
+          <t>Наклейки на кубики</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>В CW контроль обозначается только пехотинцем поверх врат</t>
+          <t>В базе CW обычные чёрные d6; кастомные кубики — только в допах</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>не задано</t>
+          <t>20 кубиков оклеено</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0 в базе</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -5781,23 +5782,23 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>акрил, ⌀20 мм</t>
+          <t>наклейки на белые чистые кубики</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>Под Акрил/06. Контроль - круглый жетон - ⌀20мм.png</t>
-        </is>
-      </c>
-      <c r="I103" s="4" t="inlineStr">
-        <is>
-          <t>требует доработки</t>
+          <t>Templates/Saved/Dices Print Sheet.pdf</t>
+        </is>
+      </c>
+      <c r="I103" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J103" s="5" t="n"/>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА. Нужно решение: оставить как маркер контроля или перерисовать в зону сети.</t>
+          <t>СВЕРХ ОРИГИНАЛА. Комплект собран.</t>
         </is>
       </c>
     </row>
@@ -5809,48 +5810,48 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Мех как отдельный тип отряда</t>
+          <t>Зоны сети + ЦУ + Рой как единая связка</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>В CW нет; ближайшее — класс Terror (CW-U5)</t>
+          <t>В CW механика разнесена: Slime Sea Overlook, Slime Molds, Filth</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>3 (Братство Сингулярности)</t>
+          <t>3–4 зоны + 1 ЦУ + Рой</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>разнесено по допам</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>док фракций v2.0</t>
+          <t>правила, §Варианты</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>миниатюра</t>
+          <t>акрил + миниатюра</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/Братство Сингулярности/</t>
-        </is>
-      </c>
-      <c r="I104" s="7" t="inlineStr">
-        <is>
-          <t>готово</t>
+          <t>Под Акрил/05 (ЦУ), Под Акрил/06 (зоны сети)</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>требует доработки</t>
         </is>
       </c>
       <c r="J104" s="5" t="n"/>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА. Строится как боевая машина, но неуязвим к эффектам против БМ.</t>
+          <t>СВЕРХ ОРИГИНАЛА по компоновке: у нас это один вариант игры с собственным набором компонентов. ЦУ и зоны сети готовы, фигурки Роя — нет.</t>
         </is>
       </c>
     </row>
@@ -5862,48 +5863,48 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Наклейки на кубики</t>
+          <t>8 фракций в одной коробке</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>В базе CW обычные чёрные d6; кастомные кубики — только в допах</t>
+          <t>В базе CW 4 фракции; ещё 7 продаются отдельными допами</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>80 наклеек (30/25/25)</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>0 в базе</t>
+          <t>4 — база</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>файл</t>
+          <t>CLAUDE.md (зафиксировано)</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>наклейки</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>Templates/Saved/Dices Print Sheet.pdf</t>
-        </is>
-      </c>
-      <c r="I105" s="4" t="inlineStr">
-        <is>
-          <t>требует доработки</t>
+          <t>Templates/Saved/Faction Card — *.pdf (8 файлов)</t>
+        </is>
+      </c>
+      <c r="I105" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J105" s="5" t="n"/>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА. На 20 кубиков нужно 120 граней — лист не покрывает комплект.</t>
+          <t>СВЕРХ ОРИГИНАЛА. Число фракций в правилах не названо — зафиксировано в CLAUDE.md.</t>
         </is>
       </c>
     </row>
@@ -5915,173 +5916,173 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Зоны сети + ЦУ + Рой как единая связка</t>
+          <t>Мех «Паладин Братства» вместо боевого робота</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>В CW механика разнесена: Slime Sea Overlook, Slime Molds, Filth</t>
+          <t>В CW фракция без Великого Древнего есть (The Ancients), но замены на 3 юнита нет</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>3–4 зоны + 1 ЦУ + Рой</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>разнесено по допам</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>правила, §Варианты</t>
+          <t>док фракций v2.0</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>акрил + миниатюра</t>
+          <t>миниатюра</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>Под Акрил/05 (ЦУ)</t>
-        </is>
-      </c>
-      <c r="I106" s="4" t="inlineStr">
-        <is>
-          <t>требует доработки</t>
+          <t>Templates/Units/Братство Сингулярности/</t>
+        </is>
+      </c>
+      <c r="I106" s="7" t="inlineStr">
+        <is>
+          <t>готово</t>
         </is>
       </c>
       <c r="J106" s="5" t="n"/>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА по компоновке: у нас это один вариант игры с собственным набором компонентов.</t>
+          <t>СВЕРХ ОРИГИНАЛА.</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>4. Сверх оригинала</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>8 фракций в одной коробке</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>В базе CW 4 фракции; ещё 7 продаются отдельными допами</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>4 — база</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="inlineStr">
-        <is>
-          <t>CLAUDE.md (зафиксировано)</t>
-        </is>
-      </c>
-      <c r="G107" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>Templates/Saved/Faction Card — *.pdf (8 файлов)</t>
-        </is>
-      </c>
-      <c r="I107" s="7" t="inlineStr">
-        <is>
-          <t>готово</t>
-        </is>
-      </c>
-      <c r="J107" s="5" t="n"/>
-      <c r="K107" s="3" t="inlineStr">
-        <is>
-          <t>СВЕРХ ОРИГИНАЛА. Число фракций в правилах не названо — зафиксировано в CLAUDE.md.</t>
-        </is>
-      </c>
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>5. Из оригинала не берём</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n"/>
+      <c r="E107" s="2" t="n"/>
+      <c r="F107" s="2" t="n"/>
+      <c r="G107" s="2" t="n"/>
+      <c r="H107" s="2" t="n"/>
+      <c r="I107" s="2" t="n"/>
+      <c r="J107" s="2" t="n"/>
+      <c r="K107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>4. Сверх оригинала</t>
+          <t>5. Из оригинала не берём</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Мех «Паладин Братства» вместо боевого робота</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>В CW фракция без Великого Древнего есть (The Ancients), но замены на 3 юнита нет</t>
+          <t>Старшие знаки как жетоны + мешочек (Elder Signs, Cloth Bag)</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36 жетонов — база</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>док фракций v2.0</t>
+          <t>решение проекта</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>миниатюра</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>Templates/Units/Братство Сингулярности/</t>
-        </is>
-      </c>
-      <c r="I108" s="7" t="inlineStr">
-        <is>
-          <t>готово</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J108" s="5" t="n"/>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>СВЕРХ ОРИГИНАЛА.</t>
+          <t>Заменено картами скрытого влияния. Жетонный вариант «в мешочке» осознанно не используется.</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>5. Из оригинала не берём</t>
         </is>
       </c>
-      <c r="B109" s="2" t="n"/>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="2" t="n"/>
-      <c r="E109" s="2" t="n"/>
-      <c r="F109" s="2" t="n"/>
-      <c r="G109" s="2" t="n"/>
-      <c r="H109" s="2" t="n"/>
-      <c r="I109" s="2" t="n"/>
-      <c r="J109" s="2" t="n"/>
-      <c r="K109" s="2" t="n"/>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>Спеллбуки как картонные жетоны-накладки (Spellbooks)</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>24 — база</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>решение проекта</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J109" s="5" t="n"/>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>Заменено картами технологий.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -6096,7 +6097,7 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Старшие знаки как жетоны + мешочек (Elder Signs, Cloth Bag)</t>
+          <t>Жетоны осквернения (Desecration Markers) — 12, только у Yellow Sign</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -6106,7 +6107,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>36 жетонов — база</t>
+          <t>12 — база</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -6132,7 +6133,7 @@
       <c r="J110" s="5" t="n"/>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>Заменено картами скрытого влияния. Жетонный вариант «в мешочке» осознанно не используется.</t>
+          <t>Уникальный компонент фракции Yellow Sign. Прямого аналога у нас нет; роль занимают вышки/общины/энграммы.</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6150,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Спеллбуки как картонные жетоны-накладки (Spellbooks)</t>
+          <t>Верховный жрец (High Priest) как отдельная фигурка сверх лидера</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -6159,7 +6160,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>24 — база</t>
+          <t>9 — доп. Onslaught 1</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -6185,7 +6186,7 @@
       <c r="J111" s="5" t="n"/>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>Заменено картами технологий.</t>
+          <t>У нас роль верховного жреца выполняет полковник (вариант игры).</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6203,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Жетоны осквернения (Desecration Markers) — 12, только у Yellow Sign</t>
+          <t>Второй маркер на фракцию (Power Marker в составе Faction Markers)</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
@@ -6212,7 +6213,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>12 — база</t>
+          <t>8 (по 2 на фракцию) — база</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -6238,7 +6239,7 @@
       <c r="J112" s="5" t="n"/>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>Уникальный компонент фракции Yellow Sign. Прямого аналога у нас нет; роль занимают вышки/общины/энграммы.</t>
+          <t>У нас маркер фракции 1, а нефть отслеживается общими маркерами нефти (10 шт.).</t>
         </is>
       </c>
     </row>
@@ -6255,7 +6256,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Верховный жрец (High Priest) как отдельная фигурка сверх лидера</t>
+          <t>Карты-дополнения: Primeval Earth, Dreamlands, Yuggoth, Celaeno, Shaggai</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -6265,7 +6266,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>9 — доп. Onslaught 1</t>
+          <t>5 карт — Onslaught 1–3</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -6291,7 +6292,7 @@
       <c r="J113" s="5" t="n"/>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>У нас роль верховного жреца выполняет полковник (вариант игры).</t>
+          <t>Механики Лаборатории и Роя перенесены с карты Yuggoth на основное поле через жетоны.</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6309,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Второй маркер на фракцию (Power Marker в составе Faction Markers)</t>
+          <t>Соборы (Cathedrals ×4, The Ancients) и Chaos Gates (×3, Daemon Sultan)</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
@@ -6318,7 +6319,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>8 (по 2 на фракцию) — база</t>
+          <t>4 / 3 — Onslaught 3 / 4</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
@@ -6344,7 +6345,7 @@
       <c r="J114" s="5" t="n"/>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>У нас маркер фракции 1, а нефть отслеживается общими маркерами нефти (10 шт.).</t>
+          <t>Ближайший аналог у нас — жетоны «Община» Братства Сингулярности (4 шт.).</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6362,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Карты-дополнения: Primeval Earth, Dreamlands, Yuggoth, Celaeno, Shaggai</t>
+          <t>Класс юнита Terror (Cosmic Terrors, CW-U5)</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -6371,7 +6372,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>5 карт — Onslaught 1–3</t>
+          <t>3 — доп. Onslaught 2</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -6397,7 +6398,7 @@
       <c r="J115" s="5" t="n"/>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>Механики Лаборатории и Роя перенесены с карты Yuggoth на основное поле через жетоны.</t>
+          <t>Иерархия рангов CW: культист &lt; монстр &lt; Terror &lt; независимый Древний &lt; Древний фракции. У нас Terror отсутствует.</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6415,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Соборы (Cathedrals ×4, The Ancients) и Chaos Gates (×3, Daemon Sultan)</t>
+          <t>Ледники (Primeval, 13 фигур), Watcher (Yuggoth), Worms of Ghroth (Shaggai)</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -6424,7 +6425,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>4 / 3 — Onslaught 3 / 4</t>
+          <t>по допам</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
@@ -6450,7 +6451,7 @@
       <c r="J116" s="5" t="n"/>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>Ближайший аналог у нас — жетоны «Община» Братства Сингулярности (4 шт.).</t>
+          <t>Неигровые угрозы на картах-дополнениях. У нас роль «глобального события» играют карты событий фабрик.</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6468,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Класс юнита Terror (Cosmic Terrors, CW-U5)</t>
+          <t>Альтернативная победа по Цитаделям (Dreamlands)</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -6477,7 +6478,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>3 — доп. Onslaught 2</t>
+          <t>4 Цитадели на карту — доп. Onslaught 1</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
@@ -6503,202 +6504,96 @@
       <c r="J117" s="5" t="n"/>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>Иерархия рангов CW: культист &lt; монстр &lt; Terror &lt; независимый Древний &lt; Древний фракции. У нас Terror отсутствует.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>5. Из оригинала не берём</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
-        <is>
-          <t>Ледники (Primeval, 13 фигур), Watcher (Yuggoth), Worms of Ghroth (Shaggai)</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>по допам</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>решение проекта</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I118" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J118" s="5" t="n"/>
-      <c r="K118" s="3" t="inlineStr">
-        <is>
-          <t>Неигровые угрозы на картах-дополнениях. У нас роль «глобального события» играют карты событий фабрик.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>5. Из оригинала не берём</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t>Альтернативная победа по Цитаделям (Dreamlands)</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="inlineStr">
-        <is>
-          <t>4 Цитадели на карту — доп. Onslaught 1</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t>решение проекта</t>
-        </is>
-      </c>
-      <c r="G119" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I119" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J119" s="5" t="n"/>
-      <c r="K119" s="3" t="inlineStr">
-        <is>
           <t>У нас единственные условия победы — 30 влияния + 6 технологий, либо Ядерная катастрофа.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>Как читать таблицу</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>Готовность (столбец J)</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>единственный столбец под ручное заполнение Alek. Выпадающий список: напечатано / подготовлено / упущено. Залит жёлтым.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>Как читать таблицу</t>
+          <t>Статус арта (столбец I)</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>готово — файл есть и пригоден к производству; требует доработки — файл есть, но к нему вопросы; не сделано — арта нет; нет носителя — не решено, из чего делать.</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="10" t="inlineStr">
-        <is>
-          <t>Готовность (столбец J)</t>
-        </is>
-      </c>
-      <c r="B123" s="11" t="inlineStr">
-        <is>
-          <t>единственный столбец под ручное заполнение Alek. Выпадающий список: напечатано / подготовлено / упущено. Залит жёлтым.</t>
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>Источник нашего числа</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>правила = черновик правил, раздел «Компоненты»; док фракций = «Нефтяные войны (фракции v.2.0)»; файл в папке = число снято с готового файла; выведено = число получено логически, в источниках его нет.</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="10" t="inlineStr">
-        <is>
-          <t>Статус арта (столбец I)</t>
-        </is>
-      </c>
-      <c r="B124" s="11" t="inlineStr">
-        <is>
-          <t>готово — файл есть и пригоден к производству; требует доработки — файл есть, но к нему вопросы; не сделано — арта нет; нет носителя — не решено, из чего делать.</t>
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>Кол-во в оригинале</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>«база» = базовая коробка Cthulhu Wars; иначе указано дополнение (Onslaught 1/2/3/4, код набора).</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="10" t="inlineStr">
-        <is>
-          <t>Источник нашего числа</t>
-        </is>
-      </c>
-      <c r="B125" s="11" t="inlineStr">
-        <is>
-          <t>правила = черновик правил, раздел «Компоненты»; док фракций = «Нефтяные войны (фракции v.2.0)»; файл в папке = число снято с готового файла; выведено = число получено логически, в источниках его нет.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="10" t="inlineStr">
-        <is>
-          <t>Кол-во в оригинале</t>
-        </is>
-      </c>
-      <c r="B126" s="11" t="inlineStr">
-        <is>
-          <t>«база» = базовая коробка Cthulhu Wars; иначе указано дополнение (Onslaught 1/2/3/4, код набора).</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="10" t="inlineStr">
+      <c r="A125" s="9" t="inlineStr">
         <is>
           <t>Конфликты</t>
         </is>
       </c>
-      <c r="B127" s="11" t="inlineStr">
+      <c r="B125" s="10" t="inlineStr">
         <is>
           <t>все расхождения между источниками вынесены на лист «Расхождения» — там же предложение и пустой столбец под решение.</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="46" customHeight="1">
-      <c r="A129" s="12" t="inlineStr">
+    <row r="127" ht="46" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
         <is>
           <t>Источники по оригинальной Cthulhu Wars: cthulhuwars.fandom.com, официальный список компонентов Petersen Games (воспроизведён на nobleknight.com), рулбук necronomicon.app/rulebook, BoardGameGeek, petersengames.com/support product list. Наши числа: черновик правил (docs.google.com/document/d/1Eb49tnE9XtmucsIQImUPP2uk2OEXHUC292uYP6iSz30), док «Фракции v2.0» (docs.google.com/document/d/13MHcSea0FDaMMRJTa989p846IqYxmg4OA0CpRvNDrek), готовые PDF в Templates/Saved и файлы в Под Акрил. Составлено 27.08.2026.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K119"/>
+  <autoFilter ref="A1:K117"/>
   <mergeCells count="6">
+    <mergeCell ref="B121:K121"/>
     <mergeCell ref="B123:K123"/>
-    <mergeCell ref="B127:K127"/>
-    <mergeCell ref="B126:K126"/>
-    <mergeCell ref="A129:K129"/>
+    <mergeCell ref="B122:K122"/>
+    <mergeCell ref="A127:K127"/>
     <mergeCell ref="B125:K125"/>
     <mergeCell ref="B124:K124"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J319" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Недопустимое значение" error="Допустимые значения: напечатано / подготовлено / упущено" promptTitle="Готовность" prompt="Заполняет Alek: напечатано / подготовлено / упущено" type="list">
+    <dataValidation sqref="J2:J317" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Недопустимое значение" error="Допустимые значения: напечатано / подготовлено / упущено" promptTitle="Готовность" prompt="Заполняет Alek: напечатано / подготовлено / упущено" type="list">
       <formula1>"напечатано,подготовлено,упущено"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6712,7 +6607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6762,7 +6657,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Жетоны «Община» (Братство Сингулярности)</t>
         </is>
@@ -6792,10 +6687,14 @@
           <t>Принять 4 жетона. Проверить, не являются ли 4 бессимвольные плитки рубашками — тогда файл корректен. Иначе урезать раскладку до 4.</t>
         </is>
       </c>
-      <c r="G2" s="5" t="n"/>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>ЗАКРЫТО. Жетоны двусторонние: 8 плиток на листе = 4 жетона. Готовы.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Жетоны «Нефтяная вышка» (Глобал Петролеум)</t>
         </is>
@@ -6828,7 +6727,7 @@
       <c r="G3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Карты скрытого влияния</t>
         </is>
@@ -6858,10 +6757,14 @@
           <t>Привести PDF к 36 картам (18/12/6) — числа совпадают с оригиналом CW. Либо явно объявить 4 карты запасными.</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n"/>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>ЗАКРЫТО. Лишние карты — намеренный запас под брак резки и печати. Рабочая колода 36. Напечатано.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Карты событий фабрик</t>
         </is>
@@ -6891,10 +6794,14 @@
           <t>Обновить правила до 8 либо сократить колоду до 6. Дубль «СБОЙ» ×2, вероятно, намеренный — подтвердить.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>ЗАКРЫТО. Напечатаны. Две лишние карты — эксперимент, в рабочую колоду не входят. Колода 6.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Терминология скрытого влияния</t>
         </is>
@@ -6927,7 +6834,7 @@
       <c r="G6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Игровое поле — «2/4 шт.»</t>
         </is>
@@ -6960,7 +6867,7 @@
       <c r="G7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Число фракций</t>
         </is>
@@ -6993,7 +6900,7 @@
       <c r="G8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Памятки — 5 шт.</t>
         </is>
@@ -7026,7 +6933,7 @@
       <c r="G9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Маркеры нефти — 10 шт.</t>
         </is>
@@ -7056,10 +6963,14 @@
           <t>Сделать 8 (по 1 на фракцию) и определить носитель — либо объяснить 10.</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>ЗАКРЫТО. Куплены пластиковые бочонки нефти.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Трек Судного дня — 2 шт.</t>
         </is>
@@ -7092,7 +7003,7 @@
       <c r="G11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Боевой робот Североамериканского Альянса</t>
         </is>
@@ -7125,7 +7036,7 @@
       <c r="G12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>6-я технология Североамериканского Альянса</t>
         </is>
@@ -7158,7 +7069,7 @@
       <c r="G13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Технология Островной Империи</t>
         </is>
@@ -7191,7 +7102,7 @@
       <c r="G14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Технология Клонэйд Ресёрч</t>
         </is>
@@ -7224,7 +7135,7 @@
       <c r="G15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Технологии Братства Сингулярности</t>
         </is>
@@ -7257,7 +7168,7 @@
       <c r="G16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Боевой робот Сайнтифик Солюшн — чужая технология</t>
         </is>
@@ -7290,7 +7201,7 @@
       <c r="G17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Написание «Шрёдингер» / «Шредингер»</t>
         </is>
@@ -7323,7 +7234,7 @@
       <c r="G18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Написание «Краб» / «C.R.A.B.»</t>
         </is>
@@ -7356,7 +7267,7 @@
       <c r="G19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Moon Systems — пехотинцы и полковник</t>
         </is>
@@ -7389,7 +7300,7 @@
       <c r="G20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Тип отряда «Пастух» (Глобал Петролеум)</t>
         </is>
@@ -7422,7 +7333,7 @@
       <c r="G21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Зоны сети — 3–4 шт.</t>
         </is>
@@ -7455,7 +7366,7 @@
       <c r="G22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Энграммы — количество</t>
         </is>
@@ -7488,7 +7399,7 @@
       <c r="G23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Лаборатория и ЦУ — количество</t>
         </is>
@@ -7521,7 +7432,7 @@
       <c r="G24" s="5" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Рой боевых дронов — количество фигурок</t>
         </is>
@@ -7554,7 +7465,7 @@
       <c r="G25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Наёмники — количество карт и фигурок</t>
         </is>
@@ -7587,7 +7498,7 @@
       <c r="G26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Дубль в правилах размещения Лаборатории</t>
         </is>
@@ -7620,7 +7531,7 @@
       <c r="G27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Название конца трека Судного дня</t>
         </is>
@@ -7653,7 +7564,7 @@
       <c r="G28" s="5" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Наклейки на кубики</t>
         </is>
@@ -7683,10 +7594,14 @@
           <t>На 20 кубиков нужно 120 граней. Уточнить, на сколько кубиков рассчитан лист, и допечатать.</t>
         </is>
       </c>
-      <c r="G29" s="5" t="n"/>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>ЗАКРЫТО. Кубики готовы: наклейки нанесены на белые чистые d6.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>Имя файла маркера Судного дня</t>
         </is>
@@ -7719,40 +7634,44 @@
       <c r="G30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>Файл «06. Контроль» — нет количества в имени</t>
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Файл «06. Контроль» — что это за компонент</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Зоны сети — 3-4 жетона вокруг Узла управления</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Не описывается</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Прямого аналога нет; ближайшее — область Slime Sea (Yuggoth)</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Под Акрил/06. Контроль - круглый жетон - ⌀20мм.png — количество в имени отсутствует; альфа-канал есть (CLAUDE.md устарел)</t>
+          <t>Под Акрил/06. Контроль - круглый жетон - ⌀20мм.png — имя вводит в заблуждение, количества в имени нет</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Определить количество (по числу фракций или по числу фабрик) и привести имя к конвенции §5.</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="n"/>
+          <t>Переименовать в «Зоны сети» и дописать количество по конвенции §5. Отдельного жетона контроля фабрик у нас нет — контроль обозначается пехотинцем поверх фабрики, как в CW.</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>ЗАКРЫТО по сути: это зоны сети для ЦУ, вариант игры с Роем. Арт готов, готовится к печати. Осталось переименовать файл.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Количество обычных фабрик в раскладке</t>
         </is>
@@ -7779,55 +7698,88 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Подтвердить, что 6 лишних — запасные, либо убрать из раскладки.</t>
+          <t>По аналогии с картами скрытого влияния 6 лишних, скорее всего, запас под брак резки и печати — подтвердить.</t>
         </is>
       </c>
       <c r="G32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>CLAUDE.md устарел по папке «Под Акрил»</t>
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Баланс сил — судьба 7-го рекрута слабого игрока</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Для сильного игрока: «Если этот рекрут когда-либо будет отправлен в запас по любой причине, вместо этого немедленно уберите его в коробку». Для слабого игрока — правила молчат</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Не описывается</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Handicap Acolyte: у слабого игрока гандикапный акольт при гибели убирается насовсем, максимум 7</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>«06. Контроль» указан как RGB без альфы — сейчас RGBA с реальной альфой; «08. Жетон первого игрока» уже существует, хотя в CLAUDE.md значится как «арта нет»; разрешения файлов 01 и 02 отличаются от записанных</t>
+          <t>Отдельного компонента нет — берётся рекрут неиспользуемой фракции (миниатюры закуплены и покрашены)</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Обновить раздел 5 и раздел 10 CLAUDE.md по фактическому состоянию.</t>
+          <t>Дописать в правила симметричное условие для слабого игрока (как в CW). Компонентов вариант не требует — вопрос чисто редакторский.</t>
         </is>
       </c>
       <c r="G33" s="5" t="n"/>
     </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>CLAUDE.md устарел по папке «Под Акрил» и по разделу «Известные проблемы»</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>«06. Контроль» указан как RGB без альфы — сейчас RGBA с реальной альфой, и это не маркер контроля, а зоны сети; «08. Жетон первого игрока» уже существует, хотя в CLAUDE.md значится как «арта нет»; разрешения файлов 01 и 02 отличаются от записанных; по тайлу «Луна» задача «перегенерировать» снята; «Общины» и карты событий помечены как проблемные, хотя готовы</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Обновить разделы 4, 5 и 10 CLAUDE.md по фактическому состоянию на 31.08.2026.</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>Столбец «Решение Alek» (G) — под ручное заполнение, залит жёлтым. «—» означает, что источник по этому компоненту молчит.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G33"/>
+  <autoFilter ref="A1:G34"/>
   <mergeCells count="1">
-    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
